--- a/2026/BRIN 3219/Marzo/BRIN3219-EXPENSAS-Marzo.xlsx
+++ b/2026/BRIN 3219/Marzo/BRIN3219-EXPENSAS-Marzo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\Marzo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{477BF6A7-03FC-4A09-A7EC-E4D21F37D904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8103A8A-2337-4ECE-8E58-68EFBAE8C778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$O$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$98</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$94</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="158">
   <si>
     <t>U.F.</t>
   </si>
@@ -468,21 +468,9 @@
     <t>REEMPLAZO</t>
   </si>
   <si>
-    <t>subidos en n0v</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ascensor </t>
   </si>
   <si>
-    <t>Reemplazo Sra. Monica</t>
-  </si>
-  <si>
-    <t>Seguro Sra. Monica</t>
-  </si>
-  <si>
-    <t>Ascensor</t>
-  </si>
-  <si>
     <t>Ordinarios:</t>
   </si>
   <si>
@@ -510,15 +498,6 @@
     <t>Sr. Abogado - Escrito para volver a solicitar la activacion de la cuenta bancaria</t>
   </si>
   <si>
-    <t>Copia de llaves - Cerrajeria</t>
-  </si>
-  <si>
-    <t>Lema -Saldo restante a abonar mes anterior (Leer expensas anteriores)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julio Doartero - Cambio de contactora de bomba - Material y mano de obra </t>
-  </si>
-  <si>
     <t>VTO: 17/04</t>
   </si>
   <si>
@@ -529,6 +508,15 @@
   </si>
   <si>
     <t>Egresos por gastos mes - MARZO</t>
+  </si>
+  <si>
+    <t>subidos en m4rz0</t>
+  </si>
+  <si>
+    <t>Reemplazo por vacaciones</t>
+  </si>
+  <si>
+    <t>Seguro - Reemplazo</t>
   </si>
 </sst>
 </file>
@@ -545,7 +533,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -757,6 +745,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1337,7 +1332,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1543,7 +1538,6 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="21" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1632,9 +1626,74 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="30" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1674,9 +1733,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1698,69 +1754,6 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1782,12 +1775,6 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="18" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1797,7 +1784,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2244,7 +2237,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.6640625" customWidth="1"/>
@@ -2269,23 +2262,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="187"/>
-      <c r="E2" s="188"/>
-      <c r="F2" s="188"/>
-      <c r="G2" s="188"/>
-      <c r="H2" s="189"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="208"/>
+      <c r="F2" s="208"/>
+      <c r="G2" s="208"/>
+      <c r="H2" s="209"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="202">
+      <c r="E3" s="221">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="202"/>
-      <c r="G3" s="202"/>
-      <c r="H3" s="203"/>
+      <c r="F3" s="221"/>
+      <c r="G3" s="221"/>
+      <c r="H3" s="222"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2332,10 +2325,10 @@
         <v>66</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -2364,14 +2357,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="199"/>
-      <c r="B12" s="200"/>
-      <c r="C12" s="200"/>
-      <c r="D12" s="200"/>
-      <c r="E12" s="200"/>
-      <c r="F12" s="200"/>
-      <c r="G12" s="200"/>
-      <c r="H12" s="201"/>
+      <c r="A12" s="219"/>
+      <c r="B12" s="186"/>
+      <c r="C12" s="186"/>
+      <c r="D12" s="186"/>
+      <c r="E12" s="186"/>
+      <c r="F12" s="186"/>
+      <c r="G12" s="186"/>
+      <c r="H12" s="220"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2384,545 +2377,541 @@
       <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="204" t="s">
+      <c r="A14" s="223" t="s">
         <v>122</v>
       </c>
-      <c r="B14" s="204"/>
-      <c r="C14" s="204"/>
-      <c r="D14" s="204"/>
-      <c r="E14" s="204"/>
-      <c r="F14" s="204"/>
-      <c r="G14" s="204"/>
-      <c r="H14" s="204"/>
+      <c r="B14" s="223"/>
+      <c r="C14" s="223"/>
+      <c r="D14" s="223"/>
+      <c r="E14" s="223"/>
+      <c r="F14" s="223"/>
+      <c r="G14" s="223"/>
+      <c r="H14" s="223"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="173" t="s">
+      <c r="A15" s="172" t="s">
         <v>137</v>
       </c>
-      <c r="B15" s="138"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
+      <c r="B15" s="137"/>
+      <c r="C15" s="137"/>
+      <c r="D15" s="137"/>
+      <c r="E15" s="137"/>
+      <c r="F15" s="137"/>
+      <c r="G15" s="137"/>
       <c r="H15" s="73">
-        <v>332232.59999999998</v>
+        <v>417468.99</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="173" t="s">
+      <c r="A16" s="172" t="s">
         <v>85</v>
       </c>
-      <c r="B16" s="138"/>
-      <c r="C16" s="138"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="138"/>
+      <c r="B16" s="137"/>
+      <c r="C16" s="137"/>
+      <c r="D16" s="137"/>
+      <c r="E16" s="137"/>
+      <c r="F16" s="137"/>
+      <c r="G16" s="137"/>
       <c r="H16" s="73">
-        <v>-52326.64</v>
+        <v>-65751.37</v>
       </c>
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="173" t="s">
+      <c r="A17" s="172" t="s">
         <v>116</v>
       </c>
-      <c r="B17" s="138"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="138"/>
+      <c r="B17" s="137"/>
+      <c r="C17" s="137"/>
+      <c r="D17" s="137"/>
+      <c r="E17" s="137"/>
+      <c r="F17" s="137"/>
+      <c r="G17" s="137"/>
       <c r="H17" s="73">
-        <v>0.04</v>
+        <v>0.38</v>
       </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="173" t="s">
+      <c r="A18" s="172" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="138"/>
-      <c r="C18" s="138"/>
-      <c r="D18" s="138"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="138"/>
+      <c r="B18" s="137"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="137"/>
       <c r="H18" s="69">
         <f>SUM(H15:H17)</f>
-        <v>279905.99999999994</v>
+        <v>351718</v>
       </c>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" spans="1:9" ht="0.75" customHeight="1">
-      <c r="A19" s="195" t="s">
+    <row r="19" spans="1:9">
+      <c r="A19" s="215" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="195"/>
-      <c r="C19" s="195"/>
-      <c r="D19" s="195"/>
-      <c r="E19" s="195"/>
-      <c r="F19" s="195"/>
-      <c r="G19" s="195"/>
-      <c r="H19" s="195"/>
-    </row>
-    <row r="20" spans="1:9" hidden="1">
-      <c r="A20" s="173" t="s">
-        <v>143</v>
-      </c>
-      <c r="B20" s="138"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="138"/>
-      <c r="F20" s="138"/>
-      <c r="G20" s="138"/>
-      <c r="H20" s="73"/>
-    </row>
-    <row r="21" spans="1:9" hidden="1">
-      <c r="A21" s="173" t="s">
-        <v>144</v>
-      </c>
-      <c r="B21" s="138"/>
-      <c r="C21" s="138"/>
-      <c r="D21" s="138"/>
-      <c r="E21" s="138"/>
-      <c r="F21" s="138"/>
-      <c r="G21" s="138"/>
-      <c r="H21" s="73"/>
-    </row>
-    <row r="22" spans="1:9" hidden="1">
-      <c r="A22" s="173" t="s">
+      <c r="B19" s="215"/>
+      <c r="C19" s="215"/>
+      <c r="D19" s="215"/>
+      <c r="E19" s="215"/>
+      <c r="F19" s="215"/>
+      <c r="G19" s="215"/>
+      <c r="H19" s="215"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="172" t="s">
+        <v>156</v>
+      </c>
+      <c r="B20" s="137"/>
+      <c r="C20" s="137"/>
+      <c r="D20" s="137"/>
+      <c r="E20" s="137"/>
+      <c r="F20" s="137"/>
+      <c r="G20" s="137"/>
+      <c r="H20" s="73">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="172" t="s">
+        <v>157</v>
+      </c>
+      <c r="B21" s="137"/>
+      <c r="C21" s="137"/>
+      <c r="D21" s="137"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="137"/>
+      <c r="G21" s="137"/>
+      <c r="H21" s="73">
+        <v>4519.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="172" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="138"/>
-      <c r="C22" s="138"/>
-      <c r="D22" s="138"/>
-      <c r="E22" s="138"/>
-      <c r="F22" s="138"/>
-      <c r="G22" s="138"/>
+      <c r="B22" s="137"/>
+      <c r="C22" s="137"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
+      <c r="G22" s="137"/>
       <c r="H22" s="69">
         <f>SUM(H20:H21)</f>
-        <v>0</v>
+        <v>56519.75</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="194" t="s">
+      <c r="A23" s="214" t="s">
         <v>127</v>
       </c>
-      <c r="B23" s="194"/>
-      <c r="C23" s="194"/>
-      <c r="D23" s="194"/>
-      <c r="E23" s="194"/>
-      <c r="F23" s="194"/>
-      <c r="G23" s="194"/>
-      <c r="H23" s="194"/>
+      <c r="B23" s="214"/>
+      <c r="C23" s="214"/>
+      <c r="D23" s="214"/>
+      <c r="E23" s="214"/>
+      <c r="F23" s="214"/>
+      <c r="G23" s="214"/>
+      <c r="H23" s="214"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="138" t="s">
+      <c r="A24" s="137" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="138"/>
-      <c r="C24" s="138"/>
-      <c r="D24" s="138"/>
-      <c r="E24" s="138"/>
-      <c r="F24" s="138"/>
-      <c r="G24" s="138"/>
+      <c r="B24" s="137"/>
+      <c r="C24" s="137"/>
+      <c r="D24" s="137"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
+      <c r="G24" s="137"/>
       <c r="H24" s="73">
         <v>32000</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="138"/>
-      <c r="B25" s="138"/>
-      <c r="C25" s="138"/>
-      <c r="D25" s="138"/>
-      <c r="E25" s="138"/>
-      <c r="F25" s="138"/>
-      <c r="G25" s="138"/>
+      <c r="A25" s="137"/>
+      <c r="B25" s="137"/>
+      <c r="C25" s="137"/>
+      <c r="D25" s="137"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
+      <c r="G25" s="137"/>
       <c r="H25" s="73"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="138" t="s">
+      <c r="A26" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="138"/>
-      <c r="C26" s="138"/>
-      <c r="D26" s="138"/>
-      <c r="E26" s="138"/>
-      <c r="F26" s="138"/>
-      <c r="G26" s="138"/>
+      <c r="B26" s="137"/>
+      <c r="C26" s="137"/>
+      <c r="D26" s="137"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="137"/>
+      <c r="G26" s="137"/>
       <c r="H26" s="69">
         <f>SUM(H24:H25)</f>
         <v>32000</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A27" s="190" t="s">
+    <row r="27" spans="1:9">
+      <c r="A27" s="210" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="190"/>
-      <c r="C27" s="190"/>
-      <c r="D27" s="190"/>
-      <c r="E27" s="190"/>
-      <c r="F27" s="190"/>
-      <c r="G27" s="190"/>
-      <c r="H27" s="190"/>
-    </row>
-    <row r="28" spans="1:9" hidden="1">
-      <c r="A28" s="173"/>
-      <c r="B28" s="138"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
+      <c r="B27" s="210"/>
+      <c r="C27" s="210"/>
+      <c r="D27" s="210"/>
+      <c r="E27" s="210"/>
+      <c r="F27" s="210"/>
+      <c r="G27" s="210"/>
+      <c r="H27" s="210"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="172"/>
+      <c r="B28" s="137"/>
+      <c r="C28" s="137"/>
+      <c r="D28" s="137"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="137"/>
+      <c r="G28" s="137"/>
       <c r="H28" s="73"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="173" t="s">
+      <c r="A29" s="172" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="174"/>
-      <c r="C29" s="138"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="138"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="241">
+      <c r="B29" s="173"/>
+      <c r="C29" s="137"/>
+      <c r="D29" s="137"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="137"/>
+      <c r="G29" s="137"/>
+      <c r="H29" s="73">
         <f>41955.11+1661.16+14950.47</f>
         <v>58566.740000000005</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="138" t="s">
+      <c r="A30" s="137" t="s">
         <v>136</v>
       </c>
-      <c r="B30" s="138"/>
-      <c r="C30" s="138"/>
-      <c r="D30" s="138"/>
-      <c r="E30" s="138"/>
-      <c r="F30" s="138"/>
-      <c r="G30" s="138"/>
+      <c r="B30" s="137"/>
+      <c r="C30" s="137"/>
+      <c r="D30" s="137"/>
+      <c r="E30" s="137"/>
+      <c r="F30" s="137"/>
+      <c r="G30" s="137"/>
       <c r="H30" s="73">
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="138" t="s">
+      <c r="A31" s="137" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="138"/>
-      <c r="C31" s="138"/>
-      <c r="D31" s="138"/>
-      <c r="E31" s="138"/>
-      <c r="F31" s="138"/>
-      <c r="G31" s="138"/>
+      <c r="B31" s="137"/>
+      <c r="C31" s="137"/>
+      <c r="D31" s="137"/>
+      <c r="E31" s="137"/>
+      <c r="F31" s="137"/>
+      <c r="G31" s="137"/>
       <c r="H31" s="69">
         <f>SUM(H28:H30)</f>
         <v>58566.740000000005</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="190" t="s">
+      <c r="A32" s="210" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="190"/>
-      <c r="C32" s="190"/>
-      <c r="D32" s="190"/>
-      <c r="E32" s="190"/>
-      <c r="F32" s="190"/>
-      <c r="G32" s="190"/>
-      <c r="H32" s="190"/>
-    </row>
-    <row r="33" spans="1:10" ht="14.25" customHeight="1">
-      <c r="A33" s="138" t="s">
+      <c r="B32" s="210"/>
+      <c r="C32" s="210"/>
+      <c r="D32" s="210"/>
+      <c r="E32" s="210"/>
+      <c r="F32" s="210"/>
+      <c r="G32" s="210"/>
+      <c r="H32" s="210"/>
+    </row>
+    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A33" s="137" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="138"/>
-      <c r="C33" s="138"/>
-      <c r="D33" s="138"/>
-      <c r="E33" s="138"/>
-      <c r="F33" s="138"/>
-      <c r="G33" s="138"/>
+      <c r="B33" s="137"/>
+      <c r="C33" s="137"/>
+      <c r="D33" s="137"/>
+      <c r="E33" s="137"/>
+      <c r="F33" s="137"/>
+      <c r="G33" s="137"/>
       <c r="H33" s="73">
-        <v>1490686.61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="175" t="s">
+        <v>1078660.6200000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="174" t="s">
         <v>98</v>
       </c>
-      <c r="B34" s="138"/>
-      <c r="C34" s="138"/>
-      <c r="D34" s="138"/>
-      <c r="E34" s="138"/>
-      <c r="F34" s="138"/>
-      <c r="G34" s="138"/>
-      <c r="H34" s="241">
+      <c r="B34" s="137"/>
+      <c r="C34" s="137"/>
+      <c r="D34" s="137"/>
+      <c r="E34" s="137"/>
+      <c r="F34" s="137"/>
+      <c r="G34" s="137"/>
+      <c r="H34" s="73">
         <v>71134.429999999993</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="138" t="s">
+    <row r="35" spans="1:11">
+      <c r="A35" s="137" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="138"/>
-      <c r="C35" s="138"/>
-      <c r="D35" s="138"/>
-      <c r="E35" s="138"/>
-      <c r="F35" s="138"/>
-      <c r="G35" s="138"/>
-      <c r="H35" s="176">
+      <c r="B35" s="137"/>
+      <c r="C35" s="137"/>
+      <c r="D35" s="137"/>
+      <c r="E35" s="137"/>
+      <c r="F35" s="137"/>
+      <c r="G35" s="137"/>
+      <c r="H35" s="175">
         <f>SUM(H33:H34)</f>
-        <v>1561821.04</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="204" t="s">
+        <v>1149795.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="223" t="s">
         <v>129</v>
       </c>
-      <c r="B36" s="204"/>
-      <c r="C36" s="204"/>
-      <c r="D36" s="204"/>
-      <c r="E36" s="204"/>
-      <c r="F36" s="204"/>
-      <c r="G36" s="204"/>
-      <c r="H36" s="204"/>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="B36" s="223"/>
+      <c r="C36" s="223"/>
+      <c r="D36" s="223"/>
+      <c r="E36" s="223"/>
+      <c r="F36" s="223"/>
+      <c r="G36" s="223"/>
+      <c r="H36" s="223"/>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="80" t="s">
         <v>68</v>
       </c>
-      <c r="B37" s="138"/>
-      <c r="C37" s="138"/>
-      <c r="D37" s="138"/>
-      <c r="E37" s="138"/>
-      <c r="F37" s="138"/>
-      <c r="G37" s="138"/>
-      <c r="H37" s="241">
+      <c r="B37" s="137"/>
+      <c r="C37" s="137"/>
+      <c r="D37" s="137"/>
+      <c r="E37" s="137"/>
+      <c r="F37" s="137"/>
+      <c r="G37" s="137"/>
+      <c r="H37" s="73">
         <v>85000</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:11">
       <c r="A38" s="80" t="s">
-        <v>156</v>
-      </c>
-      <c r="B38" s="138"/>
-      <c r="C38" s="138"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
+        <v>145</v>
+      </c>
+      <c r="B38" s="137"/>
+      <c r="C38" s="137"/>
+      <c r="D38" s="137"/>
+      <c r="E38" s="137"/>
+      <c r="F38" s="137"/>
+      <c r="G38" s="137"/>
       <c r="H38" s="73">
-        <v>170591.71</v>
-      </c>
-      <c r="I38" s="184"/>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="80" t="s">
+        <v>200000</v>
+      </c>
+      <c r="I38" s="7"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="137" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="137"/>
+      <c r="C39" s="137"/>
+      <c r="D39" s="137"/>
+      <c r="E39" s="137"/>
+      <c r="F39" s="137"/>
+      <c r="G39" s="137"/>
+      <c r="H39" s="73">
+        <v>24285.72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="137" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" s="137"/>
+      <c r="C40" s="137"/>
+      <c r="D40" s="137"/>
+      <c r="E40" s="137"/>
+      <c r="F40" s="137"/>
+      <c r="G40" s="137"/>
+      <c r="H40" s="73">
+        <v>65000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="137" t="s">
         <v>149</v>
       </c>
-      <c r="B39" s="138"/>
-      <c r="C39" s="138"/>
-      <c r="D39" s="138"/>
-      <c r="E39" s="138"/>
-      <c r="F39" s="138"/>
-      <c r="G39" s="138"/>
-      <c r="H39" s="73">
-        <v>0</v>
-      </c>
-      <c r="I39" s="7"/>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40" s="138" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" s="138"/>
-      <c r="C40" s="138"/>
-      <c r="D40" s="138"/>
-      <c r="E40" s="138"/>
-      <c r="F40" s="138"/>
-      <c r="G40" s="138"/>
-      <c r="H40" s="241">
-        <v>24285.72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41" s="138" t="s">
-        <v>160</v>
-      </c>
-      <c r="B41" s="138"/>
-      <c r="C41" s="138"/>
-      <c r="D41" s="138"/>
-      <c r="E41" s="138"/>
-      <c r="F41" s="138"/>
-      <c r="G41" s="138"/>
-      <c r="H41" s="241">
-        <v>65000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42" s="138" t="s">
-        <v>153</v>
-      </c>
-      <c r="B42" s="138"/>
-      <c r="C42" s="138"/>
-      <c r="D42" s="138"/>
-      <c r="E42" s="138"/>
-      <c r="F42" s="138"/>
-      <c r="G42" s="138"/>
-      <c r="H42" s="73">
-        <v>47200</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43" s="138" t="s">
-        <v>153</v>
-      </c>
-      <c r="B43" s="138"/>
-      <c r="C43" s="138"/>
-      <c r="D43" s="138"/>
-      <c r="E43" s="138"/>
-      <c r="F43" s="138"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="73">
-        <v>50700</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44" s="80" t="s">
+      <c r="B41" s="137"/>
+      <c r="C41" s="137"/>
+      <c r="D41" s="137"/>
+      <c r="E41" s="137"/>
+      <c r="F41" s="137"/>
+      <c r="G41" s="137"/>
+      <c r="H41" s="73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="137" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="137"/>
+      <c r="C42" s="137"/>
+      <c r="D42" s="137"/>
+      <c r="E42" s="137"/>
+      <c r="F42" s="137"/>
+      <c r="G42" s="137"/>
+      <c r="H42" s="69">
+        <f>SUM(H37:H41)</f>
+        <v>374285.72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="223" t="s">
+        <v>130</v>
+      </c>
+      <c r="B43" s="223"/>
+      <c r="C43" s="223"/>
+      <c r="D43" s="223"/>
+      <c r="E43" s="223"/>
+      <c r="F43" s="223"/>
+      <c r="G43" s="223"/>
+      <c r="H43" s="223"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="137" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" s="137"/>
+      <c r="C44" s="137"/>
+      <c r="D44" s="137"/>
+      <c r="E44" s="137"/>
+      <c r="F44" s="137"/>
+      <c r="G44" s="137"/>
+      <c r="H44" s="73">
+        <v>189700</v>
+      </c>
+      <c r="J44" t="s">
         <v>155</v>
       </c>
-      <c r="B44" s="138"/>
-      <c r="C44" s="138"/>
-      <c r="D44" s="138"/>
-      <c r="E44" s="138"/>
-      <c r="F44" s="138"/>
-      <c r="G44" s="138"/>
-      <c r="H44" s="73">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45" s="80" t="s">
-        <v>157</v>
-      </c>
-      <c r="B45" s="138"/>
-      <c r="C45" s="138"/>
-      <c r="D45" s="138"/>
-      <c r="E45" s="138"/>
-      <c r="F45" s="138"/>
-      <c r="G45" s="138"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="137" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="137"/>
+      <c r="C45" s="137"/>
+      <c r="D45" s="137"/>
+      <c r="E45" s="137"/>
+      <c r="F45" s="137"/>
+      <c r="G45" s="137"/>
       <c r="H45" s="73">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46" s="138" t="s">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="137" t="s">
+        <v>72</v>
+      </c>
+      <c r="B46" s="137"/>
+      <c r="C46" s="137"/>
+      <c r="D46" s="137"/>
+      <c r="E46" s="137"/>
+      <c r="F46" s="137"/>
+      <c r="G46" s="137"/>
+      <c r="H46" s="175">
+        <f>SUM(H44:H45)</f>
+        <v>234700</v>
+      </c>
+      <c r="K46" s="7"/>
+    </row>
+    <row r="47" spans="1:11" s="6" customFormat="1">
+      <c r="A47" s="224" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="225"/>
+      <c r="C47" s="225"/>
+      <c r="D47" s="225"/>
+      <c r="E47" s="225"/>
+      <c r="F47" s="225"/>
+      <c r="G47" s="225"/>
+      <c r="H47" s="226"/>
+    </row>
+    <row r="48" spans="1:11" s="6" customFormat="1">
+      <c r="A48" s="80" t="s">
+        <v>117</v>
+      </c>
+      <c r="B48" s="80"/>
+      <c r="C48" s="80"/>
+      <c r="D48" s="80"/>
+      <c r="E48" s="80"/>
+      <c r="F48" s="80"/>
+      <c r="G48" s="80"/>
+      <c r="H48" s="73">
+        <v>26307</v>
+      </c>
+      <c r="I48" s="60"/>
+    </row>
+    <row r="49" spans="1:9" s="6" customFormat="1">
+      <c r="A49" s="80" t="s">
         <v>73</v>
       </c>
-      <c r="B46" s="138"/>
-      <c r="C46" s="138"/>
-      <c r="D46" s="138"/>
-      <c r="E46" s="138"/>
-      <c r="F46" s="138"/>
-      <c r="G46" s="138"/>
-      <c r="H46" s="69">
-        <f>SUM(H37:H45)</f>
-        <v>702777.42999999993</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47" s="204" t="s">
-        <v>130</v>
-      </c>
-      <c r="B47" s="204"/>
-      <c r="C47" s="204"/>
-      <c r="D47" s="204"/>
-      <c r="E47" s="204"/>
-      <c r="F47" s="204"/>
-      <c r="G47" s="204"/>
-      <c r="H47" s="204"/>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48" s="138" t="s">
-        <v>70</v>
-      </c>
-      <c r="B48" s="138"/>
-      <c r="C48" s="138"/>
-      <c r="D48" s="138"/>
-      <c r="E48" s="138"/>
-      <c r="F48" s="138"/>
-      <c r="G48" s="138"/>
-      <c r="H48" s="73">
-        <v>170100</v>
-      </c>
-      <c r="J48" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="138" t="s">
-        <v>115</v>
-      </c>
-      <c r="B49" s="138"/>
-      <c r="C49" s="138"/>
-      <c r="D49" s="138"/>
-      <c r="E49" s="138"/>
-      <c r="F49" s="138"/>
-      <c r="G49" s="138"/>
-      <c r="H49" s="241">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="138" t="s">
-        <v>72</v>
-      </c>
-      <c r="B50" s="138"/>
-      <c r="C50" s="138"/>
-      <c r="D50" s="138"/>
-      <c r="E50" s="138"/>
-      <c r="F50" s="138"/>
-      <c r="G50" s="138"/>
-      <c r="H50" s="176">
-        <f>SUM(H48:H49)</f>
-        <v>215100</v>
-      </c>
-      <c r="K50" s="7"/>
-    </row>
-    <row r="51" spans="1:11" s="6" customFormat="1">
-      <c r="A51" s="205" t="s">
-        <v>131</v>
-      </c>
-      <c r="B51" s="206"/>
-      <c r="C51" s="206"/>
-      <c r="D51" s="206"/>
-      <c r="E51" s="206"/>
-      <c r="F51" s="206"/>
-      <c r="G51" s="206"/>
-      <c r="H51" s="207"/>
-    </row>
-    <row r="52" spans="1:11" s="6" customFormat="1">
-      <c r="A52" s="80" t="s">
-        <v>117</v>
-      </c>
+      <c r="B49" s="80"/>
+      <c r="C49" s="80"/>
+      <c r="D49" s="80"/>
+      <c r="E49" s="80"/>
+      <c r="F49" s="80"/>
+      <c r="G49" s="80"/>
+      <c r="H49" s="69">
+        <f>SUM(H48)</f>
+        <v>26307</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="6" customFormat="1">
+      <c r="A50" s="223" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="223"/>
+      <c r="C50" s="223"/>
+      <c r="D50" s="223"/>
+      <c r="E50" s="223"/>
+      <c r="F50" s="223"/>
+      <c r="G50" s="223"/>
+      <c r="H50" s="223"/>
+    </row>
+    <row r="51" spans="1:9" s="6" customFormat="1">
+      <c r="A51" s="80" t="s">
+        <v>150</v>
+      </c>
+      <c r="B51" s="80"/>
+      <c r="C51" s="80"/>
+      <c r="D51" s="80"/>
+      <c r="E51" s="80"/>
+      <c r="F51" s="80"/>
+      <c r="G51" s="80"/>
+      <c r="H51" s="73">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="6" customFormat="1">
+      <c r="A52" s="80"/>
       <c r="B52" s="80"/>
       <c r="C52" s="80"/>
       <c r="D52" s="80"/>
       <c r="E52" s="80"/>
       <c r="F52" s="80"/>
       <c r="G52" s="80"/>
-      <c r="H52" s="73">
-        <v>24990</v>
-      </c>
-      <c r="I52" s="60"/>
-    </row>
-    <row r="53" spans="1:11" s="6" customFormat="1">
-      <c r="A53" s="80" t="s">
-        <v>73</v>
-      </c>
+      <c r="H52" s="73"/>
+    </row>
+    <row r="53" spans="1:9" s="6" customFormat="1">
+      <c r="A53" s="80"/>
       <c r="B53" s="80"/>
       <c r="C53" s="80"/>
       <c r="D53" s="80"/>
@@ -2930,643 +2919,594 @@
       <c r="F53" s="80"/>
       <c r="G53" s="80"/>
       <c r="H53" s="69">
-        <f>SUM(H52)</f>
-        <v>24990</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="204" t="s">
-        <v>132</v>
-      </c>
-      <c r="B54" s="204"/>
-      <c r="C54" s="204"/>
-      <c r="D54" s="204"/>
-      <c r="E54" s="204"/>
-      <c r="F54" s="204"/>
-      <c r="G54" s="204"/>
-      <c r="H54" s="204"/>
-    </row>
-    <row r="55" spans="1:11" s="6" customFormat="1">
-      <c r="A55" s="80" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A54" s="80" t="s">
+        <v>74</v>
+      </c>
+      <c r="B54" s="80"/>
+      <c r="C54" s="80"/>
+      <c r="D54" s="80"/>
+      <c r="E54" s="80"/>
+      <c r="F54" s="80"/>
+      <c r="G54" s="80"/>
+      <c r="H54" s="69">
+        <f>SUM(H51:H53)</f>
+        <v>100000</v>
+      </c>
+      <c r="I54" s="60"/>
+    </row>
+    <row r="55" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A55" s="224"/>
+      <c r="B55" s="225"/>
+      <c r="C55" s="225"/>
+      <c r="D55" s="225"/>
+      <c r="E55" s="225"/>
+      <c r="F55" s="225"/>
+      <c r="G55" s="225"/>
+      <c r="H55" s="226"/>
+    </row>
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A56" s="81"/>
+      <c r="B56" s="82"/>
+      <c r="C56" s="82"/>
+      <c r="D56" s="82"/>
+      <c r="E56" s="82"/>
+      <c r="F56" s="82"/>
+      <c r="G56" s="82"/>
+      <c r="H56" s="156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A57" s="157"/>
+      <c r="B57" s="158"/>
+      <c r="C57" s="158"/>
+      <c r="D57" s="158"/>
+      <c r="E57" s="158"/>
+      <c r="F57" s="158"/>
+      <c r="G57" s="158"/>
+      <c r="H57" s="159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A58" s="160"/>
+      <c r="B58" s="161"/>
+      <c r="C58" s="161"/>
+      <c r="D58" s="161"/>
+      <c r="E58" s="161"/>
+      <c r="F58" s="161"/>
+      <c r="G58" s="161"/>
+      <c r="H58" s="156">
+        <f>H56+H57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A59" s="202" t="s">
+        <v>80</v>
+      </c>
+      <c r="B59" s="203"/>
+      <c r="C59" s="203"/>
+      <c r="D59" s="203"/>
+      <c r="E59" s="203"/>
+      <c r="F59" s="203"/>
+      <c r="G59" s="203"/>
+      <c r="H59" s="162">
+        <f>H54</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A60" s="205"/>
+      <c r="B60" s="205"/>
+      <c r="C60" s="205"/>
+      <c r="D60" s="205"/>
+      <c r="E60" s="205"/>
+      <c r="F60" s="205"/>
+      <c r="G60" s="205"/>
+      <c r="H60" s="205"/>
+    </row>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A61" s="206"/>
+      <c r="B61" s="206"/>
+      <c r="C61" s="206"/>
+      <c r="D61" s="206"/>
+      <c r="E61" s="206"/>
+      <c r="F61" s="206"/>
+      <c r="G61" s="206"/>
+      <c r="H61" s="206"/>
+    </row>
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A62" s="204" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="204"/>
+      <c r="C62" s="204"/>
+      <c r="D62" s="204"/>
+      <c r="E62" s="204"/>
+      <c r="F62" s="204"/>
+      <c r="G62" s="204"/>
+      <c r="H62" s="163"/>
+    </row>
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A63" s="216"/>
+      <c r="B63" s="217"/>
+      <c r="C63" s="217"/>
+      <c r="D63" s="217"/>
+      <c r="E63" s="217"/>
+      <c r="F63" s="217"/>
+      <c r="G63" s="218"/>
+      <c r="H63" s="73"/>
+    </row>
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A64" s="127" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="80"/>
+      <c r="C64" s="80"/>
+      <c r="D64" s="80"/>
+      <c r="E64" s="80"/>
+      <c r="F64" s="80"/>
+      <c r="G64" s="80"/>
+      <c r="H64" s="69">
+        <f>SUM(H63:H63)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A65" s="128"/>
+      <c r="B65" s="128"/>
+      <c r="C65" s="128"/>
+      <c r="D65" s="128"/>
+      <c r="E65" s="128"/>
+      <c r="F65" s="128"/>
+      <c r="G65" s="128"/>
+      <c r="H65" s="129"/>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A66" s="193" t="s">
+        <v>81</v>
+      </c>
+      <c r="B66" s="194"/>
+      <c r="C66" s="194"/>
+      <c r="D66" s="194"/>
+      <c r="E66" s="194"/>
+      <c r="F66" s="194"/>
+      <c r="G66" s="194"/>
+      <c r="H66" s="130">
+        <f>H64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A67" s="211" t="s">
+        <v>87</v>
+      </c>
+      <c r="B67" s="212"/>
+      <c r="C67" s="212"/>
+      <c r="D67" s="212"/>
+      <c r="E67" s="212"/>
+      <c r="F67" s="212"/>
+      <c r="G67" s="213"/>
+      <c r="H67" s="130"/>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A68" s="211" t="s">
+        <v>92</v>
+      </c>
+      <c r="B68" s="212"/>
+      <c r="C68" s="212"/>
+      <c r="D68" s="212"/>
+      <c r="E68" s="212"/>
+      <c r="F68" s="212"/>
+      <c r="G68" s="213"/>
+      <c r="H68" s="130"/>
+    </row>
+    <row r="69" spans="1:11" ht="18">
+      <c r="A69" s="193" t="s">
+        <v>88</v>
+      </c>
+      <c r="B69" s="194"/>
+      <c r="C69" s="194"/>
+      <c r="D69" s="194"/>
+      <c r="E69" s="194"/>
+      <c r="F69" s="194"/>
+      <c r="G69" s="194"/>
+      <c r="H69" s="130">
+        <f>H26+H35+H42+H46+H49+H31+H18+H22</f>
+        <v>2283892.2599999998</v>
+      </c>
+      <c r="J69" s="171"/>
+      <c r="K69" s="142"/>
+    </row>
+    <row r="70" spans="1:11" ht="18">
+      <c r="A70" s="199" t="s">
+        <v>120</v>
+      </c>
+      <c r="B70" s="200"/>
+      <c r="C70" s="200"/>
+      <c r="D70" s="200"/>
+      <c r="E70" s="200"/>
+      <c r="F70" s="200"/>
+      <c r="G70" s="201"/>
+      <c r="H70" s="131">
+        <f>H67+H69</f>
+        <v>2283892.2599999998</v>
+      </c>
+      <c r="I70" s="126"/>
+      <c r="J70" s="185"/>
+      <c r="K70" s="185"/>
+    </row>
+    <row r="71" spans="1:11" ht="18">
+      <c r="A71" s="199" t="s">
+        <v>93</v>
+      </c>
+      <c r="B71" s="200"/>
+      <c r="C71" s="200"/>
+      <c r="D71" s="200"/>
+      <c r="E71" s="200"/>
+      <c r="F71" s="200"/>
+      <c r="G71" s="201"/>
+      <c r="H71" s="132">
+        <f>H68+H66</f>
+        <v>0</v>
+      </c>
+      <c r="J71" s="142"/>
+    </row>
+    <row r="72" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A72" s="197" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="198"/>
+      <c r="C72" s="198"/>
+      <c r="D72" s="198"/>
+      <c r="E72" s="198"/>
+      <c r="F72" s="198"/>
+      <c r="G72" s="198"/>
+      <c r="H72" s="133">
+        <f>H69+H66</f>
+        <v>2283892.2599999998</v>
+      </c>
+      <c r="J72" s="7"/>
+    </row>
+    <row r="73" spans="1:11" ht="18" hidden="1">
+      <c r="A73" s="195" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" s="196"/>
+      <c r="C73" s="196"/>
+      <c r="D73" s="196"/>
+      <c r="E73" s="196"/>
+      <c r="F73" s="196"/>
+      <c r="G73" s="196"/>
+      <c r="H73" s="134">
+        <f>H58</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="7"/>
+    </row>
+    <row r="74" spans="1:11" ht="18" hidden="1">
+      <c r="A74" s="135"/>
+      <c r="B74" s="135"/>
+      <c r="C74" s="135"/>
+      <c r="D74" s="135"/>
+      <c r="E74" s="135"/>
+      <c r="F74" s="135"/>
+      <c r="G74" s="135"/>
+      <c r="H74" s="136"/>
+      <c r="J74" s="7"/>
+    </row>
+    <row r="75" spans="1:11" ht="18" hidden="1">
+      <c r="A75" s="135"/>
+      <c r="B75" s="135"/>
+      <c r="C75" s="135"/>
+      <c r="D75" s="135"/>
+      <c r="E75" s="135"/>
+      <c r="F75" s="135"/>
+      <c r="G75" s="135"/>
+      <c r="H75" s="136"/>
+      <c r="J75" s="7"/>
+    </row>
+    <row r="76" spans="1:11" ht="18" hidden="1">
+      <c r="A76" s="135"/>
+      <c r="B76" s="135"/>
+      <c r="C76" s="135"/>
+      <c r="D76" s="135"/>
+      <c r="E76" s="135"/>
+      <c r="F76" s="135"/>
+      <c r="G76" s="135"/>
+      <c r="H76" s="136"/>
+      <c r="J76" s="7"/>
+    </row>
+    <row r="77" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A77" s="137"/>
+      <c r="B77" s="137"/>
+      <c r="C77" s="137"/>
+      <c r="D77" s="137"/>
+      <c r="E77" s="137"/>
+      <c r="F77" s="137"/>
+      <c r="G77" s="137"/>
+      <c r="H77" s="137"/>
+    </row>
+    <row r="78" spans="1:11" ht="18">
+      <c r="A78" s="190" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78" s="191"/>
+      <c r="C78" s="191"/>
+      <c r="D78" s="191"/>
+      <c r="E78" s="191"/>
+      <c r="F78" s="191"/>
+      <c r="G78" s="191"/>
+      <c r="H78" s="192"/>
+    </row>
+    <row r="79" spans="1:11" ht="18">
+      <c r="A79" s="138" t="s">
+        <v>12</v>
+      </c>
+      <c r="B79" s="139"/>
+      <c r="C79" s="139"/>
+      <c r="D79" s="139"/>
+      <c r="E79" s="139"/>
+      <c r="F79" s="139"/>
+      <c r="G79" s="139"/>
+      <c r="H79" s="140">
+        <v>4813257.659039462</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="81" t="s">
+        <v>147</v>
+      </c>
+      <c r="B80" s="82"/>
+      <c r="C80" s="82"/>
+      <c r="D80" s="82"/>
+      <c r="E80" s="82"/>
+      <c r="F80" s="82"/>
+      <c r="G80" s="82"/>
+      <c r="H80" s="141">
+        <f>Planilla!G32</f>
+        <v>4691108.2961447304</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="78" t="s">
         <v>154</v>
       </c>
-      <c r="B55" s="80"/>
-      <c r="C55" s="80"/>
-      <c r="D55" s="80"/>
-      <c r="E55" s="80"/>
-      <c r="F55" s="80"/>
-      <c r="G55" s="80"/>
-      <c r="H55" s="73">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" s="6" customFormat="1">
-      <c r="A56" s="80"/>
-      <c r="B56" s="80"/>
-      <c r="C56" s="80"/>
-      <c r="D56" s="80"/>
-      <c r="E56" s="80"/>
-      <c r="F56" s="80"/>
-      <c r="G56" s="80"/>
-      <c r="H56" s="73"/>
-    </row>
-    <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="80"/>
-      <c r="B57" s="80"/>
-      <c r="C57" s="80"/>
-      <c r="D57" s="80"/>
-      <c r="E57" s="80"/>
-      <c r="F57" s="80"/>
-      <c r="G57" s="80"/>
-      <c r="H57" s="69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A58" s="80" t="s">
-        <v>74</v>
-      </c>
-      <c r="B58" s="80"/>
-      <c r="C58" s="80"/>
-      <c r="D58" s="80"/>
-      <c r="E58" s="80"/>
-      <c r="F58" s="80"/>
-      <c r="G58" s="80"/>
-      <c r="H58" s="69">
-        <f>SUM(H55:H57)</f>
-        <v>100000</v>
-      </c>
-      <c r="I58" s="60"/>
-    </row>
-    <row r="59" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A59" s="205"/>
-      <c r="B59" s="206"/>
-      <c r="C59" s="206"/>
-      <c r="D59" s="206"/>
-      <c r="E59" s="206"/>
-      <c r="F59" s="206"/>
-      <c r="G59" s="206"/>
-      <c r="H59" s="207"/>
-    </row>
-    <row r="60" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A60" s="81"/>
-      <c r="B60" s="82"/>
-      <c r="C60" s="82"/>
-      <c r="D60" s="82"/>
-      <c r="E60" s="82"/>
-      <c r="F60" s="82"/>
-      <c r="G60" s="82"/>
-      <c r="H60" s="157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A61" s="158"/>
-      <c r="B61" s="159"/>
-      <c r="C61" s="159"/>
-      <c r="D61" s="159"/>
-      <c r="E61" s="159"/>
-      <c r="F61" s="159"/>
-      <c r="G61" s="159"/>
-      <c r="H61" s="160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A62" s="161"/>
-      <c r="B62" s="162"/>
-      <c r="C62" s="162"/>
-      <c r="D62" s="162"/>
-      <c r="E62" s="162"/>
-      <c r="F62" s="162"/>
-      <c r="G62" s="162"/>
-      <c r="H62" s="157">
-        <f>H60+H61</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A63" s="211" t="s">
-        <v>80</v>
-      </c>
-      <c r="B63" s="212"/>
-      <c r="C63" s="212"/>
-      <c r="D63" s="212"/>
-      <c r="E63" s="212"/>
-      <c r="F63" s="212"/>
-      <c r="G63" s="212"/>
-      <c r="H63" s="163">
-        <f>H58</f>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="216"/>
-      <c r="B64" s="216"/>
-      <c r="C64" s="216"/>
-      <c r="D64" s="216"/>
-      <c r="E64" s="216"/>
-      <c r="F64" s="216"/>
-      <c r="G64" s="216"/>
-      <c r="H64" s="216"/>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A65" s="217"/>
-      <c r="B65" s="217"/>
-      <c r="C65" s="217"/>
-      <c r="D65" s="217"/>
-      <c r="E65" s="217"/>
-      <c r="F65" s="217"/>
-      <c r="G65" s="217"/>
-      <c r="H65" s="217"/>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A66" s="215" t="s">
-        <v>82</v>
-      </c>
-      <c r="B66" s="215"/>
-      <c r="C66" s="215"/>
-      <c r="D66" s="215"/>
-      <c r="E66" s="215"/>
-      <c r="F66" s="215"/>
-      <c r="G66" s="215"/>
-      <c r="H66" s="164"/>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A67" s="196"/>
-      <c r="B67" s="197"/>
-      <c r="C67" s="197"/>
-      <c r="D67" s="197"/>
-      <c r="E67" s="197"/>
-      <c r="F67" s="197"/>
-      <c r="G67" s="198"/>
-      <c r="H67" s="73"/>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A68" s="128" t="s">
-        <v>73</v>
-      </c>
-      <c r="B68" s="80"/>
-      <c r="C68" s="80"/>
-      <c r="D68" s="80"/>
-      <c r="E68" s="80"/>
-      <c r="F68" s="80"/>
-      <c r="G68" s="80"/>
-      <c r="H68" s="69">
-        <f>SUM(H67:H67)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A69" s="129"/>
-      <c r="B69" s="129"/>
-      <c r="C69" s="129"/>
-      <c r="D69" s="129"/>
-      <c r="E69" s="129"/>
-      <c r="F69" s="129"/>
-      <c r="G69" s="129"/>
-      <c r="H69" s="130"/>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A70" s="213" t="s">
-        <v>81</v>
-      </c>
-      <c r="B70" s="214"/>
-      <c r="C70" s="214"/>
-      <c r="D70" s="214"/>
-      <c r="E70" s="214"/>
-      <c r="F70" s="214"/>
-      <c r="G70" s="214"/>
-      <c r="H70" s="131">
-        <f>H68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A71" s="191" t="s">
-        <v>87</v>
-      </c>
-      <c r="B71" s="192"/>
-      <c r="C71" s="192"/>
-      <c r="D71" s="192"/>
-      <c r="E71" s="192"/>
-      <c r="F71" s="192"/>
-      <c r="G71" s="193"/>
-      <c r="H71" s="131"/>
-    </row>
-    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A72" s="191" t="s">
-        <v>92</v>
-      </c>
-      <c r="B72" s="192"/>
-      <c r="C72" s="192"/>
-      <c r="D72" s="192"/>
-      <c r="E72" s="192"/>
-      <c r="F72" s="192"/>
-      <c r="G72" s="193"/>
-      <c r="H72" s="131">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="18">
-      <c r="A73" s="213" t="s">
-        <v>88</v>
-      </c>
-      <c r="B73" s="214"/>
-      <c r="C73" s="214"/>
-      <c r="D73" s="214"/>
-      <c r="E73" s="214"/>
-      <c r="F73" s="214"/>
-      <c r="G73" s="214"/>
-      <c r="H73" s="131">
-        <f>H26+H35+H46+H50+H53+H31+H18+H22</f>
-        <v>2875161.21</v>
-      </c>
-      <c r="J73" s="172"/>
-      <c r="K73" s="143"/>
-    </row>
-    <row r="74" spans="1:11" ht="18">
-      <c r="A74" s="208" t="s">
-        <v>120</v>
-      </c>
-      <c r="B74" s="209"/>
-      <c r="C74" s="209"/>
-      <c r="D74" s="209"/>
-      <c r="E74" s="209"/>
-      <c r="F74" s="209"/>
-      <c r="G74" s="210"/>
-      <c r="H74" s="132">
-        <f>H71+H73</f>
-        <v>2875161.21</v>
-      </c>
-      <c r="I74" s="127"/>
-      <c r="J74" s="218"/>
-      <c r="K74" s="218"/>
-    </row>
-    <row r="75" spans="1:11" ht="18">
-      <c r="A75" s="208" t="s">
-        <v>93</v>
-      </c>
-      <c r="B75" s="209"/>
-      <c r="C75" s="209"/>
-      <c r="D75" s="209"/>
-      <c r="E75" s="209"/>
-      <c r="F75" s="209"/>
-      <c r="G75" s="210"/>
-      <c r="H75" s="133">
-        <f>H72+H70</f>
-        <v>1000000</v>
-      </c>
-      <c r="J75" s="143"/>
-    </row>
-    <row r="76" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A76" s="227" t="s">
-        <v>83</v>
-      </c>
-      <c r="B76" s="228"/>
-      <c r="C76" s="228"/>
-      <c r="D76" s="228"/>
-      <c r="E76" s="228"/>
-      <c r="F76" s="228"/>
-      <c r="G76" s="228"/>
-      <c r="H76" s="134">
-        <f>H73+H70</f>
-        <v>2875161.21</v>
-      </c>
-      <c r="J76" s="7"/>
-    </row>
-    <row r="77" spans="1:11" ht="18" hidden="1">
-      <c r="A77" s="225" t="s">
-        <v>17</v>
-      </c>
-      <c r="B77" s="226"/>
-      <c r="C77" s="226"/>
-      <c r="D77" s="226"/>
-      <c r="E77" s="226"/>
-      <c r="F77" s="226"/>
-      <c r="G77" s="226"/>
-      <c r="H77" s="135">
-        <f>H62</f>
-        <v>0</v>
-      </c>
-      <c r="J77" s="7"/>
-    </row>
-    <row r="78" spans="1:11" ht="18" hidden="1">
-      <c r="A78" s="136"/>
-      <c r="B78" s="136"/>
-      <c r="C78" s="136"/>
-      <c r="D78" s="136"/>
-      <c r="E78" s="136"/>
-      <c r="F78" s="136"/>
-      <c r="G78" s="136"/>
-      <c r="H78" s="137"/>
-      <c r="J78" s="7"/>
-    </row>
-    <row r="79" spans="1:11" ht="18" hidden="1">
-      <c r="A79" s="136"/>
-      <c r="B79" s="136"/>
-      <c r="C79" s="136"/>
-      <c r="D79" s="136"/>
-      <c r="E79" s="136"/>
-      <c r="F79" s="136"/>
-      <c r="G79" s="136"/>
-      <c r="H79" s="137"/>
-      <c r="J79" s="7"/>
-    </row>
-    <row r="80" spans="1:11" ht="18" hidden="1">
-      <c r="A80" s="136"/>
-      <c r="B80" s="136"/>
-      <c r="C80" s="136"/>
-      <c r="D80" s="136"/>
-      <c r="E80" s="136"/>
-      <c r="F80" s="136"/>
-      <c r="G80" s="136"/>
-      <c r="H80" s="137"/>
-      <c r="J80" s="7"/>
-    </row>
-    <row r="81" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A81" s="138"/>
-      <c r="B81" s="138"/>
-      <c r="C81" s="138"/>
-      <c r="D81" s="138"/>
-      <c r="E81" s="138"/>
-      <c r="F81" s="138"/>
-      <c r="G81" s="138"/>
-      <c r="H81" s="138"/>
-    </row>
-    <row r="82" spans="1:11" ht="18">
-      <c r="A82" s="222" t="s">
-        <v>10</v>
-      </c>
-      <c r="B82" s="223"/>
-      <c r="C82" s="223"/>
-      <c r="D82" s="223"/>
-      <c r="E82" s="223"/>
-      <c r="F82" s="223"/>
-      <c r="G82" s="223"/>
-      <c r="H82" s="224"/>
-    </row>
-    <row r="83" spans="1:11" ht="18">
-      <c r="A83" s="139" t="s">
+      <c r="B81" s="79"/>
+      <c r="C81" s="79"/>
+      <c r="D81" s="79"/>
+      <c r="E81" s="79"/>
+      <c r="F81" s="79"/>
+      <c r="G81" s="79"/>
+      <c r="H81" s="179">
+        <f>-(H72)</f>
+        <v>-2283892.2599999998</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82" s="79"/>
+      <c r="C82" s="79"/>
+      <c r="D82" s="79"/>
+      <c r="E82" s="79"/>
+      <c r="F82" s="79"/>
+      <c r="G82" s="79"/>
+      <c r="H82" s="179">
+        <f>-H59</f>
+        <v>-100000</v>
+      </c>
+      <c r="K82" s="6"/>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" s="78" t="s">
+        <v>146</v>
+      </c>
+      <c r="B83" s="79"/>
+      <c r="C83" s="79"/>
+      <c r="D83" s="79"/>
+      <c r="E83" s="79"/>
+      <c r="F83" s="79"/>
+      <c r="G83" s="79"/>
+      <c r="H83" s="121">
+        <v>133680</v>
+      </c>
+      <c r="J83" s="7"/>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="B84" s="79"/>
+      <c r="C84" s="79"/>
+      <c r="D84" s="79"/>
+      <c r="E84" s="79"/>
+      <c r="F84" s="79"/>
+      <c r="G84" s="79"/>
+      <c r="H84" s="121">
+        <v>75293.599727499997</v>
+      </c>
+      <c r="I84" s="142"/>
+      <c r="J84" s="7"/>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B85" s="83"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="4"/>
+      <c r="H85" s="98"/>
+    </row>
+    <row r="86" spans="1:11" ht="18">
+      <c r="A86" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" s="23"/>
+      <c r="C86" s="23"/>
+      <c r="D86" s="23"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="23"/>
+      <c r="G86" s="23"/>
+      <c r="H86" s="84">
+        <f>SUM(H79:H85)</f>
+        <v>7329447.2949116919</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="15" thickBot="1"/>
+    <row r="88" spans="1:11" ht="16.2" thickBot="1">
+      <c r="A88" s="187" t="s">
+        <v>97</v>
+      </c>
+      <c r="B88" s="188"/>
+      <c r="C88" s="188"/>
+      <c r="D88" s="188"/>
+      <c r="E88" s="188"/>
+      <c r="F88" s="188"/>
+      <c r="G88" s="188"/>
+      <c r="H88" s="189"/>
+    </row>
+    <row r="89" spans="1:11" ht="15.6">
+      <c r="A89" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="B83" s="140"/>
-      <c r="C83" s="140"/>
-      <c r="D83" s="140"/>
-      <c r="E83" s="140"/>
-      <c r="F83" s="140"/>
-      <c r="G83" s="140"/>
-      <c r="H83" s="141">
-        <v>3564156.5524669625</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84" s="81" t="s">
-        <v>151</v>
-      </c>
-      <c r="B84" s="82"/>
-      <c r="C84" s="82"/>
-      <c r="D84" s="82"/>
-      <c r="E84" s="82"/>
-      <c r="F84" s="82"/>
-      <c r="G84" s="82"/>
-      <c r="H84" s="142">
-        <f>Planilla!G32</f>
-        <v>4001448.7106899992</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" s="78" t="s">
-        <v>161</v>
-      </c>
-      <c r="B85" s="79"/>
-      <c r="C85" s="79"/>
-      <c r="D85" s="79"/>
-      <c r="E85" s="79"/>
-      <c r="F85" s="79"/>
-      <c r="G85" s="79"/>
-      <c r="H85" s="180">
-        <f>-(H76)</f>
-        <v>-2875161.21</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="B86" s="79"/>
-      <c r="C86" s="79"/>
-      <c r="D86" s="79"/>
-      <c r="E86" s="79"/>
-      <c r="F86" s="79"/>
-      <c r="G86" s="79"/>
-      <c r="H86" s="180">
-        <f>-H63</f>
-        <v>-100000</v>
-      </c>
-      <c r="K86" s="6"/>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="78" t="s">
-        <v>150</v>
-      </c>
-      <c r="B87" s="79"/>
-      <c r="C87" s="79"/>
-      <c r="D87" s="79"/>
-      <c r="E87" s="79"/>
-      <c r="F87" s="79"/>
-      <c r="G87" s="79"/>
-      <c r="H87" s="122">
-        <v>133680</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" s="78" t="s">
-        <v>71</v>
-      </c>
-      <c r="B88" s="79"/>
-      <c r="C88" s="79"/>
-      <c r="D88" s="79"/>
-      <c r="E88" s="79"/>
-      <c r="F88" s="79"/>
-      <c r="G88" s="79"/>
-      <c r="H88" s="122">
-        <v>53562.275882499991</v>
-      </c>
-      <c r="I88" s="143"/>
-    </row>
-    <row r="89" spans="1:11">
-      <c r="A89" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="B89" s="83"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="98"/>
-    </row>
-    <row r="90" spans="1:11" ht="18">
-      <c r="A90" s="22" t="s">
+      <c r="B89" s="87"/>
+      <c r="C89" s="87"/>
+      <c r="D89" s="87"/>
+      <c r="E89" s="87"/>
+      <c r="F89" s="87"/>
+      <c r="G89" s="87"/>
+      <c r="H89" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="61" t="s">
+        <v>119</v>
+      </c>
+      <c r="B90" s="91"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="61"/>
+      <c r="E90" s="61"/>
+      <c r="F90" s="61"/>
+      <c r="G90" s="61"/>
+      <c r="H90" s="125"/>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="61"/>
+      <c r="B91" s="97"/>
+      <c r="C91" s="61"/>
+      <c r="D91" s="61"/>
+      <c r="E91" s="61"/>
+      <c r="F91" s="61"/>
+      <c r="G91" s="61"/>
+      <c r="H91" s="21"/>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="61"/>
+      <c r="B92" s="61"/>
+      <c r="C92" s="61"/>
+      <c r="D92" s="61"/>
+      <c r="E92" s="61"/>
+      <c r="F92" s="61"/>
+      <c r="G92" s="61"/>
+      <c r="H92" s="21"/>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B90" s="23"/>
-      <c r="C90" s="23"/>
-      <c r="D90" s="23"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="84">
-        <f>SUM(H83:H89)</f>
-        <v>4777686.3290394619</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="15" thickBot="1"/>
-    <row r="92" spans="1:11" ht="16.2" thickBot="1">
-      <c r="A92" s="219" t="s">
-        <v>97</v>
-      </c>
-      <c r="B92" s="220"/>
-      <c r="C92" s="220"/>
-      <c r="D92" s="220"/>
-      <c r="E92" s="220"/>
-      <c r="F92" s="220"/>
-      <c r="G92" s="220"/>
-      <c r="H92" s="221"/>
-    </row>
-    <row r="93" spans="1:11" ht="15.6">
-      <c r="A93" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B93" s="87"/>
-      <c r="C93" s="87"/>
-      <c r="D93" s="87"/>
-      <c r="E93" s="87"/>
-      <c r="F93" s="87"/>
-      <c r="G93" s="87"/>
-      <c r="H93" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="61" t="s">
-        <v>119</v>
-      </c>
-      <c r="B94" s="91"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="126"/>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="61"/>
-      <c r="B95" s="97"/>
-      <c r="C95" s="61"/>
-      <c r="D95" s="61"/>
-      <c r="E95" s="61"/>
-      <c r="F95" s="61"/>
-      <c r="G95" s="61"/>
-      <c r="H95" s="21"/>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="61"/>
-      <c r="B96" s="61"/>
-      <c r="C96" s="61"/>
-      <c r="D96" s="61"/>
-      <c r="E96" s="61"/>
-      <c r="F96" s="61"/>
-      <c r="G96" s="61"/>
-      <c r="H96" s="21"/>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="B97" s="85"/>
-      <c r="C97" s="85"/>
-      <c r="D97" s="85"/>
-      <c r="E97" s="85"/>
-      <c r="F97" s="85"/>
-      <c r="G97" s="85"/>
-      <c r="H97" s="86">
-        <f>SUM(H93:H96)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" hidden="1">
-      <c r="A100" s="200"/>
-      <c r="B100" s="200"/>
-      <c r="C100" s="200"/>
-      <c r="D100" s="200"/>
-      <c r="E100" s="200"/>
-      <c r="F100" s="200"/>
-      <c r="G100" s="200"/>
-      <c r="H100" s="200"/>
-    </row>
-    <row r="101" spans="1:8" hidden="1">
-      <c r="A101" s="200"/>
-      <c r="B101" s="200"/>
-      <c r="C101" s="200"/>
-      <c r="D101" s="200"/>
-      <c r="E101" s="200"/>
-      <c r="F101" s="200"/>
-      <c r="G101" s="200"/>
-      <c r="H101" s="200"/>
-    </row>
-    <row r="102" spans="1:8" hidden="1">
-      <c r="A102" s="200"/>
-      <c r="B102" s="200"/>
-      <c r="C102" s="200"/>
-      <c r="D102" s="200"/>
-      <c r="E102" s="200"/>
-      <c r="F102" s="200"/>
-      <c r="G102" s="200"/>
-      <c r="H102" s="200"/>
-    </row>
-    <row r="103" spans="1:8" hidden="1">
-      <c r="A103" s="200"/>
-      <c r="B103" s="200"/>
-      <c r="C103" s="200"/>
-      <c r="D103" s="200"/>
-      <c r="E103" s="200"/>
-      <c r="F103" s="200"/>
-      <c r="G103" s="200"/>
-      <c r="H103" s="200"/>
+      <c r="B93" s="85"/>
+      <c r="C93" s="85"/>
+      <c r="D93" s="85"/>
+      <c r="E93" s="85"/>
+      <c r="F93" s="85"/>
+      <c r="G93" s="85"/>
+      <c r="H93" s="86">
+        <f>SUM(H89:H92)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" hidden="1">
+      <c r="A96" s="186"/>
+      <c r="B96" s="186"/>
+      <c r="C96" s="186"/>
+      <c r="D96" s="186"/>
+      <c r="E96" s="186"/>
+      <c r="F96" s="186"/>
+      <c r="G96" s="186"/>
+      <c r="H96" s="186"/>
+    </row>
+    <row r="97" spans="1:8" hidden="1">
+      <c r="A97" s="186"/>
+      <c r="B97" s="186"/>
+      <c r="C97" s="186"/>
+      <c r="D97" s="186"/>
+      <c r="E97" s="186"/>
+      <c r="F97" s="186"/>
+      <c r="G97" s="186"/>
+      <c r="H97" s="186"/>
+    </row>
+    <row r="98" spans="1:8" hidden="1">
+      <c r="A98" s="186"/>
+      <c r="B98" s="186"/>
+      <c r="C98" s="186"/>
+      <c r="D98" s="186"/>
+      <c r="E98" s="186"/>
+      <c r="F98" s="186"/>
+      <c r="G98" s="186"/>
+      <c r="H98" s="186"/>
+    </row>
+    <row r="99" spans="1:8" hidden="1">
+      <c r="A99" s="186"/>
+      <c r="B99" s="186"/>
+      <c r="C99" s="186"/>
+      <c r="D99" s="186"/>
+      <c r="E99" s="186"/>
+      <c r="F99" s="186"/>
+      <c r="G99" s="186"/>
+      <c r="H99" s="186"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="A100:H103"/>
-    <mergeCell ref="A92:H92"/>
-    <mergeCell ref="A82:H82"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A63:G63"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A64:H65"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A68:G68"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A63:G63"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A43:H43"/>
     <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A60:H61"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="J70:K70"/>
+    <mergeCell ref="A96:H99"/>
+    <mergeCell ref="A88:H88"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A72:G72"/>
     <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A70:G70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3589,7 +3529,7 @@
     <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
     <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.77734375" style="2" customWidth="1"/>
     <col min="13" max="13" width="14.5546875" customWidth="1"/>
     <col min="14" max="14" width="13.44140625" customWidth="1"/>
     <col min="15" max="15" width="15.109375" customWidth="1"/>
@@ -3625,8 +3565,8 @@
     <row r="2" spans="1:17">
       <c r="A2" s="61"/>
       <c r="B2" s="61"/>
-      <c r="C2" s="125">
-        <v>170591.71</v>
+      <c r="C2" s="124">
+        <v>2283892.2599999998</v>
       </c>
       <c r="D2" s="61"/>
       <c r="E2" s="61"/>
@@ -3665,14 +3605,17 @@
     <row r="4" spans="1:17" ht="18.75" customHeight="1">
       <c r="A4" s="118"/>
       <c r="B4" s="119" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
       <c r="E4" s="119" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="121"/>
+      <c r="F4" s="239">
+        <f>106000-330-20+2</f>
+        <v>105652</v>
+      </c>
       <c r="G4" s="117"/>
       <c r="H4" s="117"/>
       <c r="I4" s="117"/>
@@ -3687,16 +3630,16 @@
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="120"/>
-      <c r="B5" s="230">
-        <f>C3-B7</f>
-        <v>3911355.83</v>
-      </c>
-      <c r="C5" s="230"/>
+      <c r="B5" s="228">
+        <f>C2</f>
+        <v>2283892.2599999998</v>
+      </c>
+      <c r="C5" s="228"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="236">
-        <v>70000</v>
-      </c>
-      <c r="F5" s="237"/>
+      <c r="E5" s="237">
+        <v>100000</v>
+      </c>
+      <c r="F5" s="238"/>
       <c r="G5" s="114"/>
       <c r="H5" s="114"/>
       <c r="I5" s="114"/>
@@ -3709,15 +3652,13 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="120"/>
-      <c r="B6" s="232" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" s="233"/>
+      <c r="B6" s="230"/>
+      <c r="C6" s="231"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="232" t="s">
-        <v>152</v>
-      </c>
-      <c r="F6" s="233"/>
+      <c r="E6" s="230" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="231"/>
       <c r="G6" s="114"/>
       <c r="H6" s="114"/>
       <c r="I6" s="114"/>
@@ -3730,16 +3671,11 @@
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
       <c r="A7" s="120"/>
-      <c r="B7" s="230">
-        <f>C2</f>
-        <v>170591.71</v>
-      </c>
-      <c r="C7" s="230"/>
+      <c r="B7" s="228"/>
+      <c r="C7" s="228"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="234">
-        <v>1000000</v>
-      </c>
-      <c r="F7" s="235"/>
+      <c r="E7" s="232"/>
+      <c r="F7" s="233"/>
       <c r="G7" s="114"/>
       <c r="H7" s="114"/>
       <c r="I7" s="114"/>
@@ -3770,7 +3706,7 @@
         <v>16</v>
       </c>
       <c r="G8" s="112" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H8" s="112" t="s">
         <v>63</v>
@@ -3781,7 +3717,7 @@
       <c r="J8" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="124" t="s">
+      <c r="K8" s="123" t="s">
         <v>125</v>
       </c>
       <c r="L8" s="109" t="s">
@@ -3791,34 +3727,34 @@
         <v>7</v>
       </c>
       <c r="N8" s="109" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O8" s="113" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1">
-      <c r="A9" s="170">
+      <c r="A9" s="169">
         <v>1</v>
       </c>
-      <c r="B9" s="166" t="s">
+      <c r="B9" s="165" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="167" t="s">
+      <c r="C9" s="166" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="167" t="s">
+      <c r="D9" s="166" t="s">
         <v>101</v>
       </c>
-      <c r="E9" s="168">
+      <c r="E9" s="167">
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="98">
-        <v>205818.87537000002</v>
-      </c>
-      <c r="G9" s="177">
-        <f>F9</f>
-        <v>205818.87537000002</v>
+        <v>205818.87536999999</v>
+      </c>
+      <c r="G9" s="176">
+        <f>F9+200000</f>
+        <v>405818.87537000002</v>
       </c>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
@@ -3830,27 +3766,27 @@
       </c>
       <c r="J9" s="68">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
-        <v>0</v>
+        <v>200000.00000000003</v>
       </c>
       <c r="K9" s="68">
         <f>F$4*E9</f>
-        <v>0</v>
+        <v>4278.9059999999999</v>
       </c>
       <c r="L9" s="68">
         <f>E$7*E9</f>
-        <v>40500</v>
-      </c>
-      <c r="M9" s="169">
+        <v>0</v>
+      </c>
+      <c r="M9" s="168">
         <f>B$5*E9</f>
-        <v>158409.911115</v>
-      </c>
-      <c r="N9" s="169">
+        <v>92497.636529999989</v>
+      </c>
+      <c r="N9" s="168">
         <f>B$7*E9</f>
-        <v>6908.9642549999999</v>
-      </c>
-      <c r="O9" s="185">
+        <v>0</v>
+      </c>
+      <c r="O9" s="183">
         <f>H9+I9-J9+K9+M9+N9+L9</f>
-        <v>205818.87536999999</v>
+        <v>-103223.45747000005</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1">
@@ -3870,7 +3806,7 @@
       <c r="F10" s="17">
         <v>329310.20059199998</v>
       </c>
-      <c r="G10" s="177">
+      <c r="G10" s="176">
         <f>F10</f>
         <v>329310.20059199998</v>
       </c>
@@ -3888,47 +3824,47 @@
       </c>
       <c r="K10" s="24">
         <f t="shared" ref="K10:K31" si="2">F$4*E10</f>
-        <v>0</v>
+        <v>6846.2495999999992</v>
       </c>
       <c r="L10" s="68">
         <f t="shared" ref="L10:L31" si="3">E$7*E10</f>
-        <v>64800</v>
+        <v>0</v>
       </c>
       <c r="M10" s="25">
         <f t="shared" ref="M10:M31" si="4">B$5*E10</f>
-        <v>253455.85778399999</v>
+        <v>147996.21844799997</v>
       </c>
       <c r="N10" s="25">
         <f t="shared" ref="N10:N31" si="5">B$7*E10</f>
-        <v>11054.342807999999</v>
-      </c>
-      <c r="O10" s="185">
+        <v>0</v>
+      </c>
+      <c r="O10" s="183">
         <f t="shared" ref="O10:O31" si="6">H10+I10-J10+K10+M10+N10+L10</f>
-        <v>329310.20059199998</v>
+        <v>154842.46804799998</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1">
-      <c r="A11" s="165">
+      <c r="A11" s="164">
         <v>3</v>
       </c>
-      <c r="B11" s="166" t="s">
+      <c r="B11" s="165" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="167" t="s">
+      <c r="C11" s="166" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="167" t="s">
+      <c r="D11" s="166" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="168">
+      <c r="E11" s="167">
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="98">
-        <v>244949.87142799998</v>
-      </c>
-      <c r="G11" s="177">
+        <v>244949.87142800001</v>
+      </c>
+      <c r="G11" s="176">
         <f>F11</f>
-        <v>244949.87142799998</v>
+        <v>244949.87142800001</v>
       </c>
       <c r="H11" s="68">
         <f t="shared" si="0"/>
@@ -3944,76 +3880,77 @@
       </c>
       <c r="K11" s="68">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5092.4264000000003</v>
       </c>
       <c r="L11" s="68">
         <f t="shared" si="3"/>
-        <v>48200</v>
-      </c>
-      <c r="M11" s="169">
+        <v>0</v>
+      </c>
+      <c r="M11" s="168">
         <f t="shared" si="4"/>
-        <v>188527.35100600001</v>
-      </c>
-      <c r="N11" s="169">
+        <v>110083.606932</v>
+      </c>
+      <c r="N11" s="168">
         <f t="shared" si="5"/>
-        <v>8222.5204219999996</v>
-      </c>
-      <c r="O11" s="185">
+        <v>0</v>
+      </c>
+      <c r="O11" s="183">
         <f t="shared" si="6"/>
-        <v>244949.87142800001</v>
-      </c>
+        <v>115176.03333199999</v>
+      </c>
+      <c r="P11" s="171"/>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1">
-      <c r="A12" s="144">
+      <c r="A12" s="143">
         <v>4</v>
       </c>
-      <c r="B12" s="156" t="s">
+      <c r="B12" s="155" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="154" t="s">
+      <c r="C12" s="153" t="s">
         <v>99</v>
       </c>
-      <c r="D12" s="154" t="s">
+      <c r="D12" s="153" t="s">
         <v>104</v>
       </c>
-      <c r="E12" s="155">
+      <c r="E12" s="154">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="F12" s="148">
-        <v>4107987.7727756742</v>
-      </c>
-      <c r="G12" s="178"/>
-      <c r="H12" s="149">
+      <c r="F12" s="147">
+        <v>4531867.5137583734</v>
+      </c>
+      <c r="G12" s="177"/>
+      <c r="H12" s="148">
         <f t="shared" si="0"/>
-        <v>4107987.7727756742</v>
-      </c>
-      <c r="I12" s="149">
+        <v>4531867.5137583734</v>
+      </c>
+      <c r="I12" s="148">
         <f t="shared" si="7"/>
-        <v>151995.54759269996</v>
-      </c>
-      <c r="J12" s="149">
+        <v>167679.09800905985</v>
+      </c>
+      <c r="J12" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12" s="149">
+      <c r="K12" s="148">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="149">
+        <v>5652.3819999999996</v>
+      </c>
+      <c r="L12" s="148">
         <f t="shared" si="3"/>
-        <v>53500</v>
-      </c>
-      <c r="M12" s="150">
+        <v>0</v>
+      </c>
+      <c r="M12" s="149">
         <f t="shared" si="4"/>
-        <v>209257.53690499999</v>
-      </c>
-      <c r="N12" s="150">
+        <v>122188.23590999999</v>
+      </c>
+      <c r="N12" s="149">
         <f t="shared" si="5"/>
-        <v>9126.6564849999995</v>
-      </c>
-      <c r="O12" s="186">
+        <v>0</v>
+      </c>
+      <c r="O12" s="184">
         <f t="shared" si="6"/>
-        <v>4531867.5137583734</v>
+        <v>4827387.2296774341</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1">
@@ -4031,11 +3968,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
-        <v>195654.98028999998</v>
-      </c>
-      <c r="G13" s="177">
+        <v>195654.98029000001</v>
+      </c>
+      <c r="G13" s="176">
         <f>F13</f>
-        <v>195654.98028999998</v>
+        <v>195654.98029000001</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
@@ -4051,23 +3988,23 @@
       </c>
       <c r="K13" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4067.6019999999999</v>
       </c>
       <c r="L13" s="68">
         <f t="shared" si="3"/>
-        <v>38500</v>
+        <v>0</v>
       </c>
       <c r="M13" s="25">
         <f t="shared" si="4"/>
-        <v>150587.19945499999</v>
+        <v>87929.852009999988</v>
       </c>
       <c r="N13" s="25">
         <f t="shared" si="5"/>
-        <v>6567.7808349999996</v>
-      </c>
-      <c r="O13" s="185">
+        <v>0</v>
+      </c>
+      <c r="O13" s="183">
         <f t="shared" si="6"/>
-        <v>195654.98029000001</v>
+        <v>91997.454009999987</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1">
@@ -4089,7 +4026,7 @@
       <c r="F14" s="17">
         <v>182441.91668600001</v>
       </c>
-      <c r="G14" s="177">
+      <c r="G14" s="176">
         <f>F14</f>
         <v>182441.91668600001</v>
       </c>
@@ -4107,23 +4044,23 @@
       </c>
       <c r="K14" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3792.9068000000002</v>
       </c>
       <c r="L14" s="68">
         <f t="shared" si="3"/>
-        <v>35900</v>
+        <v>0</v>
       </c>
       <c r="M14" s="25">
         <f t="shared" si="4"/>
-        <v>140417.67429700002</v>
+        <v>81991.732133999991</v>
       </c>
       <c r="N14" s="25">
         <f t="shared" si="5"/>
-        <v>6124.242389</v>
-      </c>
-      <c r="O14" s="185">
+        <v>0</v>
+      </c>
+      <c r="O14" s="183">
         <f t="shared" si="6"/>
-        <v>182441.91668600001</v>
+        <v>85784.638933999988</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1">
@@ -4143,11 +4080,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>156136.77765</v>
-      </c>
-      <c r="G15" s="177">
+        <v>203330.13136200001</v>
+      </c>
+      <c r="G15" s="176">
         <f>F15</f>
-        <v>156136.77765</v>
+        <v>203330.13136200001</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
@@ -4163,24 +4100,24 @@
       </c>
       <c r="K15" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4373.9928</v>
       </c>
       <c r="L15" s="68">
         <f t="shared" si="3"/>
-        <v>41400</v>
+        <v>0</v>
       </c>
       <c r="M15" s="25">
         <f t="shared" si="4"/>
-        <v>161930.13136200001</v>
+        <v>94553.139563999983</v>
       </c>
       <c r="N15" s="25">
         <v>0</v>
       </c>
-      <c r="O15" s="185">
+      <c r="O15" s="183">
         <f t="shared" si="6"/>
-        <v>203330.13136200001</v>
-      </c>
-      <c r="Q15" s="181"/>
+        <v>98927.13236399999</v>
+      </c>
+      <c r="Q15" s="180"/>
     </row>
     <row r="16" spans="1:17" ht="15" customHeight="1">
       <c r="A16" s="51">
@@ -4201,7 +4138,7 @@
       <c r="F16" s="17">
         <v>271884.19338999997</v>
       </c>
-      <c r="G16" s="177">
+      <c r="G16" s="176">
         <f>F16</f>
         <v>271884.19338999997</v>
       </c>
@@ -4219,25 +4156,25 @@
       </c>
       <c r="K16" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5652.3819999999996</v>
       </c>
       <c r="L16" s="68">
         <f t="shared" si="3"/>
-        <v>53500</v>
+        <v>0</v>
       </c>
       <c r="M16" s="25">
         <f t="shared" si="4"/>
-        <v>209257.53690499999</v>
+        <v>122188.23590999999</v>
       </c>
       <c r="N16" s="25">
         <f t="shared" si="5"/>
-        <v>9126.6564849999995</v>
-      </c>
-      <c r="O16" s="185">
+        <v>0</v>
+      </c>
+      <c r="O16" s="183">
         <f t="shared" si="6"/>
-        <v>271884.19338999997</v>
-      </c>
-      <c r="Q16" s="181"/>
+        <v>127840.61790999999</v>
+      </c>
+      <c r="Q16" s="180"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1">
       <c r="A17" s="51">
@@ -4256,16 +4193,19 @@
         <v>3.85E-2</v>
       </c>
       <c r="F17" s="17">
-        <v>195654.98028999998</v>
-      </c>
-      <c r="G17" s="177"/>
+        <v>398549.19485072995</v>
+      </c>
+      <c r="G17" s="176">
+        <f>F17</f>
+        <v>398549.19485072995</v>
+      </c>
       <c r="H17" s="24">
         <f t="shared" si="0"/>
-        <v>195654.98028999998</v>
+        <v>0</v>
       </c>
       <c r="I17" s="24">
         <f t="shared" si="7"/>
-        <v>7239.2342707300004</v>
+        <v>0</v>
       </c>
       <c r="J17" s="24">
         <f t="shared" si="1"/>
@@ -4273,28 +4213,28 @@
       </c>
       <c r="K17" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4067.6019999999999</v>
       </c>
       <c r="L17" s="68">
         <f t="shared" si="3"/>
-        <v>38500</v>
+        <v>0</v>
       </c>
       <c r="M17" s="25">
         <f t="shared" si="4"/>
-        <v>150587.19945499999</v>
+        <v>87929.852009999988</v>
       </c>
       <c r="N17" s="25">
         <f t="shared" si="5"/>
-        <v>6567.7808349999996</v>
-      </c>
-      <c r="O17" s="185">
+        <v>0</v>
+      </c>
+      <c r="O17" s="183">
         <f t="shared" si="6"/>
-        <v>398549.19485072995</v>
-      </c>
-      <c r="Q17" s="181"/>
+        <v>91997.454009999987</v>
+      </c>
+      <c r="Q17" s="180"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1">
-      <c r="A18" s="165">
+      <c r="A18" s="164">
         <v>10</v>
       </c>
       <c r="B18" s="42" t="s">
@@ -4303,24 +4243,24 @@
       <c r="C18" s="94" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="167"/>
-      <c r="E18" s="168">
+      <c r="D18" s="166"/>
+      <c r="E18" s="167">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="98">
-        <v>321264.60253506317</v>
-      </c>
-      <c r="G18" s="177">
-        <f>RESUMEN!H49+RESUMEN!H41+RESUMEN!H37</f>
+        <v>313378.30951486056</v>
+      </c>
+      <c r="G18" s="176">
+        <f>RESUMEN!H40+RESUMEN!H37+RESUMEN!H45</f>
         <v>195000</v>
       </c>
       <c r="H18" s="68">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>126264.60253506317</v>
+        <v>118378.30951486056</v>
       </c>
       <c r="I18" s="68">
         <f t="shared" si="7"/>
-        <v>4671.7902937973377</v>
+        <v>4379.9974520498417</v>
       </c>
       <c r="J18" s="68">
         <f t="shared" si="1"/>
@@ -4328,79 +4268,79 @@
       </c>
       <c r="K18" s="68">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3792.9068000000002</v>
       </c>
       <c r="L18" s="68">
         <f t="shared" si="3"/>
-        <v>35900</v>
-      </c>
-      <c r="M18" s="169">
+        <v>0</v>
+      </c>
+      <c r="M18" s="168">
         <f t="shared" si="4"/>
-        <v>140417.67429700002</v>
-      </c>
-      <c r="N18" s="169">
+        <v>81991.732133999991</v>
+      </c>
+      <c r="N18" s="168">
         <f t="shared" si="5"/>
-        <v>6124.242389</v>
-      </c>
-      <c r="O18" s="185">
+        <v>0</v>
+      </c>
+      <c r="O18" s="183">
         <f t="shared" si="6"/>
-        <v>313378.30951486056</v>
-      </c>
-      <c r="Q18" s="181"/>
+        <v>208542.94590091039</v>
+      </c>
+      <c r="Q18" s="180"/>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1">
-      <c r="A19" s="144">
+      <c r="A19" s="143">
         <v>11</v>
       </c>
-      <c r="B19" s="151" t="s">
+      <c r="B19" s="150" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="152" t="s">
+      <c r="C19" s="151" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="154" t="s">
+      <c r="D19" s="153" t="s">
         <v>109</v>
       </c>
-      <c r="E19" s="155">
+      <c r="E19" s="154">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F19" s="148">
-        <v>2865140.14929508</v>
-      </c>
-      <c r="G19" s="178"/>
-      <c r="H19" s="149">
+      <c r="F19" s="147">
+        <v>3181542.9629749977</v>
+      </c>
+      <c r="G19" s="177"/>
+      <c r="H19" s="148">
         <f t="shared" si="0"/>
-        <v>2865140.14929508</v>
-      </c>
-      <c r="I19" s="149">
+        <v>3181542.9629749977</v>
+      </c>
+      <c r="I19" s="148">
         <f t="shared" si="7"/>
-        <v>106010.18552391797</v>
-      </c>
-      <c r="J19" s="149">
+        <v>117717.08963007493</v>
+      </c>
+      <c r="J19" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="149">
+      <c r="K19" s="148">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="149">
+        <v>4373.9928</v>
+      </c>
+      <c r="L19" s="148">
         <f t="shared" si="3"/>
-        <v>41400</v>
-      </c>
-      <c r="M19" s="150">
+        <v>0</v>
+      </c>
+      <c r="M19" s="149">
         <f t="shared" si="4"/>
-        <v>161930.13136200001</v>
-      </c>
-      <c r="N19" s="150">
+        <v>94553.139563999983</v>
+      </c>
+      <c r="N19" s="149">
         <f t="shared" si="5"/>
-        <v>7062.4967939999997</v>
-      </c>
-      <c r="O19" s="186">
+        <v>0</v>
+      </c>
+      <c r="O19" s="184">
         <f t="shared" si="6"/>
-        <v>3181542.9629749977</v>
-      </c>
-      <c r="Q19" s="181"/>
+        <v>3398187.1849690727</v>
+      </c>
+      <c r="Q19" s="180"/>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1">
       <c r="A20" s="51">
@@ -4421,7 +4361,7 @@
       <c r="F20" s="17">
         <v>271884.19338999997</v>
       </c>
-      <c r="G20" s="177">
+      <c r="G20" s="176">
         <f>F20</f>
         <v>271884.19338999997</v>
       </c>
@@ -4439,81 +4379,81 @@
       </c>
       <c r="K20" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5652.3819999999996</v>
       </c>
       <c r="L20" s="68">
         <f t="shared" si="3"/>
-        <v>53500</v>
+        <v>0</v>
       </c>
       <c r="M20" s="25">
         <f t="shared" si="4"/>
-        <v>209257.53690499999</v>
+        <v>122188.23590999999</v>
       </c>
       <c r="N20" s="25">
         <f t="shared" si="5"/>
-        <v>9126.6564849999995</v>
-      </c>
-      <c r="O20" s="185">
+        <v>0</v>
+      </c>
+      <c r="O20" s="183">
         <f t="shared" si="6"/>
-        <v>271884.19338999997</v>
-      </c>
-      <c r="Q20" s="181"/>
+        <v>127840.61790999999</v>
+      </c>
+      <c r="Q20" s="180"/>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1">
-      <c r="A21" s="144">
+      <c r="A21" s="143">
         <v>13</v>
       </c>
-      <c r="B21" s="151" t="s">
+      <c r="B21" s="150" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="152" t="s">
+      <c r="C21" s="151" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="152" t="s">
+      <c r="D21" s="151" t="s">
         <v>133</v>
       </c>
-      <c r="E21" s="153">
+      <c r="E21" s="152">
         <v>3.85E-2</v>
       </c>
-      <c r="F21" s="148">
-        <v>1289888.3046149821</v>
-      </c>
-      <c r="G21" s="179">
-        <v>106699.66</v>
-      </c>
-      <c r="H21" s="149">
+      <c r="F21" s="147">
+        <v>1422621.6047557367</v>
+      </c>
+      <c r="G21" s="178">
+        <v>150587.20000000001</v>
+      </c>
+      <c r="H21" s="148">
         <f t="shared" si="0"/>
-        <v>1183188.6446149822</v>
-      </c>
-      <c r="I21" s="149">
+        <v>1272034.4047557367</v>
+      </c>
+      <c r="I21" s="148">
         <f t="shared" si="7"/>
-        <v>43777.979850754346</v>
-      </c>
-      <c r="J21" s="149">
+        <v>47065.272975962267</v>
+      </c>
+      <c r="J21" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K21" s="149">
+      <c r="K21" s="148">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="149">
+        <v>4067.6019999999999</v>
+      </c>
+      <c r="L21" s="148">
         <f t="shared" si="3"/>
-        <v>38500</v>
-      </c>
-      <c r="M21" s="150">
+        <v>0</v>
+      </c>
+      <c r="M21" s="149">
         <f t="shared" si="4"/>
-        <v>150587.19945499999</v>
-      </c>
-      <c r="N21" s="150">
+        <v>87929.852009999988</v>
+      </c>
+      <c r="N21" s="149">
         <f t="shared" si="5"/>
-        <v>6567.7808349999996</v>
-      </c>
-      <c r="O21" s="186">
+        <v>0</v>
+      </c>
+      <c r="O21" s="184">
         <f t="shared" si="6"/>
-        <v>1422621.6047557367</v>
-      </c>
-      <c r="Q21" s="181"/>
+        <v>1411097.1317416991</v>
+      </c>
+      <c r="Q21" s="180"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1">
       <c r="A22" s="51">
@@ -4534,7 +4474,7 @@
       <c r="F22" s="17">
         <v>182441.91668600001</v>
       </c>
-      <c r="G22" s="177">
+      <c r="G22" s="176">
         <f>F22</f>
         <v>182441.91668600001</v>
       </c>
@@ -4552,25 +4492,25 @@
       </c>
       <c r="K22" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3792.9068000000002</v>
       </c>
       <c r="L22" s="68">
         <f t="shared" si="3"/>
-        <v>35900</v>
+        <v>0</v>
       </c>
       <c r="M22" s="25">
         <f t="shared" si="4"/>
-        <v>140417.67429700002</v>
+        <v>81991.732133999991</v>
       </c>
       <c r="N22" s="25">
         <f t="shared" si="5"/>
-        <v>6124.242389</v>
-      </c>
-      <c r="O22" s="185">
+        <v>0</v>
+      </c>
+      <c r="O22" s="183">
         <f t="shared" si="6"/>
-        <v>182441.91668600001</v>
-      </c>
-      <c r="Q22" s="181"/>
+        <v>85784.638933999988</v>
+      </c>
+      <c r="Q22" s="180"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1">
       <c r="A23" s="51">
@@ -4589,11 +4529,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F23" s="17">
-        <v>210392.62815599999</v>
-      </c>
-      <c r="G23" s="177">
-        <f>114736+95655.86+1</f>
-        <v>210392.86</v>
+        <v>210392.39631200003</v>
+      </c>
+      <c r="G23" s="176">
+        <f>F23</f>
+        <v>210392.39631200003</v>
       </c>
       <c r="H23" s="24">
         <f t="shared" si="0"/>
@@ -4605,29 +4545,29 @@
       </c>
       <c r="J23" s="24">
         <f t="shared" si="1"/>
-        <v>0.23184399999445304</v>
+        <v>0</v>
       </c>
       <c r="K23" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4373.9928</v>
       </c>
       <c r="L23" s="68">
         <f t="shared" si="3"/>
-        <v>41400</v>
+        <v>0</v>
       </c>
       <c r="M23" s="25">
         <f t="shared" si="4"/>
-        <v>161930.13136200001</v>
+        <v>94553.139563999983</v>
       </c>
       <c r="N23" s="25">
         <f t="shared" si="5"/>
-        <v>7062.4967939999997</v>
-      </c>
-      <c r="O23" s="185">
+        <v>0</v>
+      </c>
+      <c r="O23" s="183">
         <f t="shared" si="6"/>
-        <v>210392.39631200003</v>
-      </c>
-      <c r="Q23" s="181"/>
+        <v>98927.13236399999</v>
+      </c>
+      <c r="Q23" s="180"/>
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1">
       <c r="A24" s="51">
@@ -4646,7 +4586,7 @@
       <c r="F24" s="17">
         <v>271884.19338999997</v>
       </c>
-      <c r="G24" s="177">
+      <c r="G24" s="176">
         <f>F24</f>
         <v>271884.19338999997</v>
       </c>
@@ -4664,25 +4604,25 @@
       </c>
       <c r="K24" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5652.3819999999996</v>
       </c>
       <c r="L24" s="68">
         <f t="shared" si="3"/>
-        <v>53500</v>
+        <v>0</v>
       </c>
       <c r="M24" s="25">
         <f t="shared" si="4"/>
-        <v>209257.53690499999</v>
+        <v>122188.23590999999</v>
       </c>
       <c r="N24" s="25">
         <f t="shared" si="5"/>
-        <v>9126.6564849999995</v>
-      </c>
-      <c r="O24" s="185">
+        <v>0</v>
+      </c>
+      <c r="O24" s="183">
         <f t="shared" si="6"/>
-        <v>271884.19338999997</v>
-      </c>
-      <c r="Q24" s="181"/>
+        <v>127840.61790999999</v>
+      </c>
+      <c r="Q24" s="180"/>
     </row>
     <row r="25" spans="1:18" s="1" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="51">
@@ -4701,11 +4641,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F25" s="17">
-        <v>195654.98028999998</v>
-      </c>
-      <c r="G25" s="177">
-        <f>106699+88955+1</f>
-        <v>195655</v>
+        <v>195654.96057999998</v>
+      </c>
+      <c r="G25" s="176">
+        <f>F25</f>
+        <v>195654.96057999998</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="0"/>
@@ -4717,29 +4657,29 @@
       </c>
       <c r="J25" s="24">
         <f t="shared" si="1"/>
-        <v>1.9710000022314489E-2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4067.6019999999999</v>
       </c>
       <c r="L25" s="68">
         <f t="shared" si="3"/>
-        <v>38500</v>
+        <v>0</v>
       </c>
       <c r="M25" s="25">
         <f t="shared" si="4"/>
-        <v>150587.19945499999</v>
+        <v>87929.852009999988</v>
       </c>
       <c r="N25" s="25">
         <f t="shared" si="5"/>
-        <v>6567.7808349999996</v>
-      </c>
-      <c r="O25" s="185">
+        <v>0</v>
+      </c>
+      <c r="O25" s="183">
         <f t="shared" si="6"/>
-        <v>195654.96057999998</v>
-      </c>
-      <c r="Q25" s="182"/>
+        <v>91997.454009999987</v>
+      </c>
+      <c r="Q25" s="181"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1">
       <c r="A26" s="51">
@@ -4758,7 +4698,7 @@
       <c r="F26" s="17">
         <v>182441.91668600001</v>
       </c>
-      <c r="G26" s="177">
+      <c r="G26" s="176">
         <f>F26</f>
         <v>182441.91668600001</v>
       </c>
@@ -4776,83 +4716,83 @@
       </c>
       <c r="K26" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3792.9068000000002</v>
       </c>
       <c r="L26" s="68">
         <f t="shared" si="3"/>
-        <v>35900</v>
+        <v>0</v>
       </c>
       <c r="M26" s="25">
         <f t="shared" si="4"/>
-        <v>140417.67429700002</v>
+        <v>81991.732133999991</v>
       </c>
       <c r="N26" s="25">
         <f t="shared" si="5"/>
-        <v>6124.242389</v>
-      </c>
-      <c r="O26" s="185">
+        <v>0</v>
+      </c>
+      <c r="O26" s="183">
         <f t="shared" si="6"/>
-        <v>182441.91668600001</v>
-      </c>
-      <c r="Q26" s="181"/>
+        <v>85784.638933999988</v>
+      </c>
+      <c r="Q26" s="180"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1">
-      <c r="A27" s="144">
+      <c r="A27" s="143">
         <v>19</v>
       </c>
-      <c r="B27" s="145" t="s">
+      <c r="B27" s="144" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="146" t="s">
+      <c r="C27" s="145" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="146" t="s">
+      <c r="D27" s="145" t="s">
         <v>124</v>
       </c>
-      <c r="E27" s="147">
+      <c r="E27" s="146">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F27" s="148">
-        <v>3164645.4340123115</v>
-      </c>
-      <c r="G27" s="178">
-        <v>210362.63</v>
-      </c>
-      <c r="H27" s="171">
+      <c r="F27" s="147">
+        <v>3273983.895916767</v>
+      </c>
+      <c r="G27" s="177">
+        <v>210392.63</v>
+      </c>
+      <c r="H27" s="170">
         <f t="shared" si="0"/>
-        <v>2954282.8040123116</v>
-      </c>
-      <c r="I27" s="149">
+        <v>3063591.2659167671</v>
+      </c>
+      <c r="I27" s="148">
         <f t="shared" si="7"/>
-        <v>109308.46374845554</v>
-      </c>
-      <c r="J27" s="149">
+        <v>113352.87683892039</v>
+      </c>
+      <c r="J27" s="148">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K27" s="149">
+      <c r="K27" s="148">
         <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L27" s="149">
+        <v>4373.9928</v>
+      </c>
+      <c r="L27" s="148">
         <f t="shared" si="3"/>
-        <v>41400</v>
-      </c>
-      <c r="M27" s="150">
+        <v>0</v>
+      </c>
+      <c r="M27" s="149">
         <f t="shared" si="4"/>
-        <v>161930.13136200001</v>
-      </c>
-      <c r="N27" s="150">
+        <v>94553.139563999983</v>
+      </c>
+      <c r="N27" s="149">
         <f t="shared" si="5"/>
-        <v>7062.4967939999997</v>
-      </c>
-      <c r="O27" s="186">
+        <v>0</v>
+      </c>
+      <c r="O27" s="184">
         <f t="shared" si="6"/>
-        <v>3273983.895916767</v>
-      </c>
-      <c r="P27" s="183">
+        <v>3275871.2751196874</v>
+      </c>
+      <c r="P27" s="182">
         <f>M27+N27</f>
-        <v>168992.62815600002</v>
+        <v>94553.139563999983</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.25" customHeight="1">
@@ -4870,16 +4810,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>1993193.5786160715</v>
-      </c>
-      <c r="G28" s="177"/>
+        <v>2338825.9344148664</v>
+      </c>
+      <c r="G28" s="176"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>1993193.5786160715</v>
+        <v>2338825.9344148664</v>
       </c>
       <c r="I28" s="24">
         <f t="shared" si="7"/>
-        <v>73748.162408794655</v>
+        <v>86536.559573350067</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
@@ -4888,19 +4828,19 @@
       <c r="K28" s="24"/>
       <c r="L28" s="68">
         <f t="shared" si="3"/>
-        <v>53500</v>
+        <v>0</v>
       </c>
       <c r="M28" s="25">
         <f t="shared" si="4"/>
-        <v>209257.53690499999</v>
+        <v>122188.23590999999</v>
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
-        <v>9126.6564849999995</v>
-      </c>
-      <c r="O28" s="185">
+        <v>0</v>
+      </c>
+      <c r="O28" s="183">
         <f t="shared" si="6"/>
-        <v>2338825.9344148664</v>
+        <v>2547550.7298982162</v>
       </c>
       <c r="P28" s="7"/>
     </row>
@@ -4919,11 +4859,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="17">
-        <v>195654.98028999998</v>
-      </c>
-      <c r="G29" s="177">
+        <v>195654.98029000001</v>
+      </c>
+      <c r="G29" s="176">
         <f>F29</f>
-        <v>195654.98028999998</v>
+        <v>195654.98029000001</v>
       </c>
       <c r="H29" s="24">
         <f t="shared" si="0"/>
@@ -4939,31 +4879,34 @@
       </c>
       <c r="K29" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4067.6019999999999</v>
       </c>
       <c r="L29" s="68">
         <f t="shared" si="3"/>
-        <v>38500</v>
+        <v>0</v>
       </c>
       <c r="M29" s="25">
         <f t="shared" si="4"/>
-        <v>150587.19945499999</v>
+        <v>87929.852009999988</v>
       </c>
       <c r="N29" s="25">
         <f t="shared" si="5"/>
-        <v>6567.7808349999996</v>
-      </c>
-      <c r="O29" s="185">
+        <v>0</v>
+      </c>
+      <c r="O29" s="183">
         <f t="shared" si="6"/>
-        <v>195654.98029000001</v>
-      </c>
-      <c r="P29" s="7"/>
+        <v>91997.454009999987</v>
+      </c>
+      <c r="P29" s="7">
+        <f>M29/2</f>
+        <v>43964.926004999994</v>
+      </c>
       <c r="Q29" s="7">
         <f>SUM(Q15:Q28)</f>
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1">
@@ -4985,7 +4928,7 @@
       <c r="F30" s="17">
         <v>182441.91668600001</v>
       </c>
-      <c r="G30" s="177">
+      <c r="G30" s="176">
         <f>F30</f>
         <v>182441.91668600001</v>
       </c>
@@ -5003,23 +4946,23 @@
       </c>
       <c r="K30" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3792.9068000000002</v>
       </c>
       <c r="L30" s="68">
         <f t="shared" si="3"/>
-        <v>35900</v>
+        <v>0</v>
       </c>
       <c r="M30" s="25">
         <f t="shared" si="4"/>
-        <v>140417.67429700002</v>
+        <v>81991.732133999991</v>
       </c>
       <c r="N30" s="25">
         <f t="shared" si="5"/>
-        <v>6124.242389</v>
-      </c>
-      <c r="O30" s="185">
+        <v>0</v>
+      </c>
+      <c r="O30" s="183">
         <f t="shared" si="6"/>
-        <v>182441.91668600001</v>
+        <v>85784.638933999988</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1">
@@ -5037,11 +4980,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="17">
-        <v>210392.62815599999</v>
-      </c>
-      <c r="G31" s="177">
+        <v>210392.62815600002</v>
+      </c>
+      <c r="G31" s="176">
         <f>F31</f>
-        <v>210392.62815599999</v>
+        <v>210392.62815600002</v>
       </c>
       <c r="H31" s="24">
         <f t="shared" si="0"/>
@@ -5057,23 +5000,23 @@
       </c>
       <c r="K31" s="24">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4373.9928</v>
       </c>
       <c r="L31" s="68">
         <f t="shared" si="3"/>
-        <v>41400</v>
+        <v>0</v>
       </c>
       <c r="M31" s="25">
         <f t="shared" si="4"/>
-        <v>161930.13136200001</v>
+        <v>94553.139563999983</v>
       </c>
       <c r="N31" s="25">
         <f t="shared" si="5"/>
-        <v>7062.4967939999997</v>
-      </c>
-      <c r="O31" s="185">
+        <v>0</v>
+      </c>
+      <c r="O31" s="183">
         <f t="shared" si="6"/>
-        <v>210392.62815600002</v>
+        <v>98927.13236399999</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15.6">
@@ -5090,157 +5033,157 @@
       </c>
       <c r="F32" s="99">
         <f>SUM(F9:F31)</f>
-        <v>17427160.99127518</v>
+        <v>18997348.68748033</v>
       </c>
       <c r="G32" s="99">
         <f>SUM(G9:G31)</f>
-        <v>4001448.7106899992</v>
-      </c>
-      <c r="H32" s="123">
+        <v>4691108.2961447304</v>
+      </c>
+      <c r="H32" s="122">
         <f>SUM(H9:H31)</f>
-        <v>13425712.532139182</v>
+        <v>14506240.391335599</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>496751.36368914973</v>
+        <v>536730.89447941736</v>
       </c>
       <c r="J32" s="99">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>0.25155400001676753</v>
+        <v>200000.00000000003</v>
       </c>
       <c r="K32" s="90">
         <f>SUM(K9:K31)</f>
-        <v>0</v>
+        <v>99999.617999999959</v>
       </c>
       <c r="L32" s="90"/>
       <c r="M32" s="54">
         <f>SUM(M9:M31)</f>
-        <v>3911355.8299999996</v>
+        <v>2283892.2599999998</v>
       </c>
       <c r="N32" s="90">
         <f>SUM(N9:N31)</f>
-        <v>163529.21320600001</v>
+        <v>0</v>
       </c>
       <c r="O32" s="54">
         <f>SUM(O9:O31)</f>
-        <v>18997348.68748033</v>
+        <v>17226863.163815022</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:15" hidden="1">
-      <c r="B34" s="229"/>
-      <c r="C34" s="229"/>
-      <c r="D34" s="229"/>
-      <c r="E34" s="229"/>
-      <c r="F34" s="229"/>
-      <c r="G34" s="229"/>
-      <c r="H34" s="229"/>
-      <c r="I34" s="229"/>
-      <c r="J34" s="229"/>
-      <c r="K34" s="229"/>
-      <c r="L34" s="229"/>
-      <c r="M34" s="229"/>
-      <c r="N34" s="229"/>
-      <c r="O34" s="229"/>
+      <c r="B34" s="227"/>
+      <c r="C34" s="227"/>
+      <c r="D34" s="227"/>
+      <c r="E34" s="227"/>
+      <c r="F34" s="227"/>
+      <c r="G34" s="227"/>
+      <c r="H34" s="227"/>
+      <c r="I34" s="227"/>
+      <c r="J34" s="227"/>
+      <c r="K34" s="227"/>
+      <c r="L34" s="227"/>
+      <c r="M34" s="227"/>
+      <c r="N34" s="227"/>
+      <c r="O34" s="227"/>
     </row>
     <row r="35" spans="1:15" hidden="1">
-      <c r="B35" s="229"/>
-      <c r="C35" s="229"/>
-      <c r="D35" s="229"/>
-      <c r="E35" s="229"/>
-      <c r="F35" s="229"/>
-      <c r="G35" s="229"/>
-      <c r="H35" s="229"/>
-      <c r="I35" s="229"/>
-      <c r="J35" s="229"/>
-      <c r="K35" s="229"/>
-      <c r="L35" s="229"/>
-      <c r="M35" s="229"/>
-      <c r="N35" s="229"/>
-      <c r="O35" s="229"/>
+      <c r="B35" s="227"/>
+      <c r="C35" s="227"/>
+      <c r="D35" s="227"/>
+      <c r="E35" s="227"/>
+      <c r="F35" s="227"/>
+      <c r="G35" s="227"/>
+      <c r="H35" s="227"/>
+      <c r="I35" s="227"/>
+      <c r="J35" s="227"/>
+      <c r="K35" s="227"/>
+      <c r="L35" s="227"/>
+      <c r="M35" s="227"/>
+      <c r="N35" s="227"/>
+      <c r="O35" s="227"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
-      <c r="B36" s="229"/>
-      <c r="C36" s="229"/>
-      <c r="D36" s="229"/>
-      <c r="E36" s="229"/>
-      <c r="F36" s="229"/>
-      <c r="G36" s="229"/>
-      <c r="H36" s="229"/>
-      <c r="I36" s="229"/>
-      <c r="J36" s="229"/>
-      <c r="K36" s="229"/>
-      <c r="L36" s="229"/>
-      <c r="M36" s="229"/>
-      <c r="N36" s="229"/>
-      <c r="O36" s="229"/>
+      <c r="B36" s="227"/>
+      <c r="C36" s="227"/>
+      <c r="D36" s="227"/>
+      <c r="E36" s="227"/>
+      <c r="F36" s="227"/>
+      <c r="G36" s="227"/>
+      <c r="H36" s="227"/>
+      <c r="I36" s="227"/>
+      <c r="J36" s="227"/>
+      <c r="K36" s="227"/>
+      <c r="L36" s="227"/>
+      <c r="M36" s="227"/>
+      <c r="N36" s="227"/>
+      <c r="O36" s="227"/>
     </row>
     <row r="37" spans="1:15" hidden="1">
-      <c r="B37" s="229"/>
-      <c r="C37" s="229"/>
-      <c r="D37" s="229"/>
-      <c r="E37" s="229"/>
-      <c r="F37" s="229"/>
-      <c r="G37" s="229"/>
-      <c r="H37" s="229"/>
-      <c r="I37" s="229"/>
-      <c r="J37" s="229"/>
-      <c r="K37" s="229"/>
-      <c r="L37" s="229"/>
-      <c r="M37" s="229"/>
-      <c r="N37" s="229"/>
-      <c r="O37" s="229"/>
+      <c r="B37" s="227"/>
+      <c r="C37" s="227"/>
+      <c r="D37" s="227"/>
+      <c r="E37" s="227"/>
+      <c r="F37" s="227"/>
+      <c r="G37" s="227"/>
+      <c r="H37" s="227"/>
+      <c r="I37" s="227"/>
+      <c r="J37" s="227"/>
+      <c r="K37" s="227"/>
+      <c r="L37" s="227"/>
+      <c r="M37" s="227"/>
+      <c r="N37" s="227"/>
+      <c r="O37" s="227"/>
     </row>
     <row r="38" spans="1:15" hidden="1">
-      <c r="A38" s="231"/>
-      <c r="B38" s="231"/>
-      <c r="C38" s="231"/>
-      <c r="D38" s="231"/>
-      <c r="E38" s="231"/>
-      <c r="F38" s="231"/>
-      <c r="G38" s="231"/>
-      <c r="H38" s="231"/>
-      <c r="I38" s="231"/>
-      <c r="J38" s="231"/>
-      <c r="K38" s="231"/>
-      <c r="L38" s="231"/>
-      <c r="M38" s="231"/>
-      <c r="N38" s="231"/>
-      <c r="O38" s="231"/>
+      <c r="A38" s="229"/>
+      <c r="B38" s="229"/>
+      <c r="C38" s="229"/>
+      <c r="D38" s="229"/>
+      <c r="E38" s="229"/>
+      <c r="F38" s="229"/>
+      <c r="G38" s="229"/>
+      <c r="H38" s="229"/>
+      <c r="I38" s="229"/>
+      <c r="J38" s="229"/>
+      <c r="K38" s="229"/>
+      <c r="L38" s="229"/>
+      <c r="M38" s="229"/>
+      <c r="N38" s="229"/>
+      <c r="O38" s="229"/>
     </row>
     <row r="39" spans="1:15" hidden="1">
-      <c r="A39" s="231"/>
-      <c r="B39" s="231"/>
-      <c r="C39" s="231"/>
-      <c r="D39" s="231"/>
-      <c r="E39" s="231"/>
-      <c r="F39" s="231"/>
-      <c r="G39" s="231"/>
-      <c r="H39" s="231"/>
-      <c r="I39" s="231"/>
-      <c r="J39" s="231"/>
-      <c r="K39" s="231"/>
-      <c r="L39" s="231"/>
-      <c r="M39" s="231"/>
-      <c r="N39" s="231"/>
-      <c r="O39" s="231"/>
+      <c r="A39" s="229"/>
+      <c r="B39" s="229"/>
+      <c r="C39" s="229"/>
+      <c r="D39" s="229"/>
+      <c r="E39" s="229"/>
+      <c r="F39" s="229"/>
+      <c r="G39" s="229"/>
+      <c r="H39" s="229"/>
+      <c r="I39" s="229"/>
+      <c r="J39" s="229"/>
+      <c r="K39" s="229"/>
+      <c r="L39" s="229"/>
+      <c r="M39" s="229"/>
+      <c r="N39" s="229"/>
+      <c r="O39" s="229"/>
     </row>
     <row r="40" spans="1:15" hidden="1">
-      <c r="A40" s="231"/>
-      <c r="B40" s="231"/>
-      <c r="C40" s="231"/>
-      <c r="D40" s="231"/>
-      <c r="E40" s="231"/>
-      <c r="F40" s="231"/>
-      <c r="G40" s="231"/>
-      <c r="H40" s="231"/>
-      <c r="I40" s="231"/>
-      <c r="J40" s="231"/>
-      <c r="K40" s="231"/>
-      <c r="L40" s="231"/>
-      <c r="M40" s="231"/>
-      <c r="N40" s="231"/>
-      <c r="O40" s="231"/>
+      <c r="A40" s="229"/>
+      <c r="B40" s="229"/>
+      <c r="C40" s="229"/>
+      <c r="D40" s="229"/>
+      <c r="E40" s="229"/>
+      <c r="F40" s="229"/>
+      <c r="G40" s="229"/>
+      <c r="H40" s="229"/>
+      <c r="I40" s="229"/>
+      <c r="J40" s="229"/>
+      <c r="K40" s="229"/>
+      <c r="L40" s="229"/>
+      <c r="M40" s="229"/>
+      <c r="N40" s="229"/>
+      <c r="O40" s="229"/>
     </row>
     <row r="41" spans="1:15">
       <c r="O41" s="7"/>
@@ -5275,15 +5218,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="238" t="s">
+      <c r="A1" s="234" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="239"/>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="240"/>
+      <c r="B1" s="235"/>
+      <c r="C1" s="235"/>
+      <c r="D1" s="235"/>
+      <c r="E1" s="235"/>
+      <c r="F1" s="235"/>
+      <c r="G1" s="236"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
